--- a/salary_data.xlsx
+++ b/salary_data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="568">
   <si>
     <t>Month</t>
   </si>
@@ -1063,17 +1063,678 @@
   </si>
   <si>
     <t>EWF</t>
+  </si>
+  <si>
+    <t>GR519</t>
+  </si>
+  <si>
+    <t>GR76</t>
+  </si>
+  <si>
+    <t>GR506</t>
+  </si>
+  <si>
+    <t>FNV1002856</t>
+  </si>
+  <si>
+    <t>GR337</t>
+  </si>
+  <si>
+    <t>GR517</t>
+  </si>
+  <si>
+    <t>GR313</t>
+  </si>
+  <si>
+    <t>GR514</t>
+  </si>
+  <si>
+    <t>FNV1001183</t>
+  </si>
+  <si>
+    <t>FNV1001659</t>
+  </si>
+  <si>
+    <t>FNV1002497</t>
+  </si>
+  <si>
+    <t>GR200</t>
+  </si>
+  <si>
+    <t>GR458</t>
+  </si>
+  <si>
+    <t>GR505</t>
+  </si>
+  <si>
+    <t>GR513</t>
+  </si>
+  <si>
+    <t>GR512</t>
+  </si>
+  <si>
+    <t>GR518</t>
+  </si>
+  <si>
+    <t>GR522</t>
+  </si>
+  <si>
+    <t>GR523</t>
+  </si>
+  <si>
+    <t>CCN1000380</t>
+  </si>
+  <si>
+    <t>CCN1001135</t>
+  </si>
+  <si>
+    <t>CCN1000148</t>
+  </si>
+  <si>
+    <t>CCN1001142</t>
+  </si>
+  <si>
+    <t>CCN1001141</t>
+  </si>
+  <si>
+    <t>CCN1001150</t>
+  </si>
+  <si>
+    <t>FNV1002905</t>
+  </si>
+  <si>
+    <t>FNV1002906</t>
+  </si>
+  <si>
+    <t>FNV1002989</t>
+  </si>
+  <si>
+    <t>FNV1002990</t>
+  </si>
+  <si>
+    <t>FNV1000360</t>
+  </si>
+  <si>
+    <t>FNV1002916</t>
+  </si>
+  <si>
+    <t>FNV1002818</t>
+  </si>
+  <si>
+    <t>FNV1002912</t>
+  </si>
+  <si>
+    <t>FNV1002979</t>
+  </si>
+  <si>
+    <t>FNV1002980</t>
+  </si>
+  <si>
+    <t>FNV1001962</t>
+  </si>
+  <si>
+    <t>FNV1002820</t>
+  </si>
+  <si>
+    <t>FNV1001622</t>
+  </si>
+  <si>
+    <t>FNV1002936</t>
+  </si>
+  <si>
+    <t>FNV1002884</t>
+  </si>
+  <si>
+    <t>FNV1002894</t>
+  </si>
+  <si>
+    <t>FNV1000630</t>
+  </si>
+  <si>
+    <t>FNV1000662</t>
+  </si>
+  <si>
+    <t>FNV1002937</t>
+  </si>
+  <si>
+    <t>FNV1002785</t>
+  </si>
+  <si>
+    <t>FNV1002786</t>
+  </si>
+  <si>
+    <t>GR413</t>
+  </si>
+  <si>
+    <t>FNV1002855</t>
+  </si>
+  <si>
+    <t>FNV1002915</t>
+  </si>
+  <si>
+    <t>FNV1002831</t>
+  </si>
+  <si>
+    <t>FNV1000346</t>
+  </si>
+  <si>
+    <t>FNV1000348</t>
+  </si>
+  <si>
+    <t>FNV1001156</t>
+  </si>
+  <si>
+    <t>FNV1001163</t>
+  </si>
+  <si>
+    <t>FNV1001227</t>
+  </si>
+  <si>
+    <t>FNV1001248</t>
+  </si>
+  <si>
+    <t>FNV1002929</t>
+  </si>
+  <si>
+    <t>FNV1002932</t>
+  </si>
+  <si>
+    <t>FNV1001981</t>
+  </si>
+  <si>
+    <t>FNV1002044</t>
+  </si>
+  <si>
+    <t>FNV1002928</t>
+  </si>
+  <si>
+    <t>FNV1002934</t>
+  </si>
+  <si>
+    <t>FNV1002935</t>
+  </si>
+  <si>
+    <t>FNV1002931</t>
+  </si>
+  <si>
+    <t>FNV1002784</t>
+  </si>
+  <si>
+    <t>FNV1002790</t>
+  </si>
+  <si>
+    <t>FNV1002904</t>
+  </si>
+  <si>
+    <t>FNV1002908</t>
+  </si>
+  <si>
+    <t>FNV1002910</t>
+  </si>
+  <si>
+    <t>FNV1002930</t>
+  </si>
+  <si>
+    <t>HARASH</t>
+  </si>
+  <si>
+    <t>Sharban kumar sahu</t>
+  </si>
+  <si>
+    <t>Sonu kumar</t>
+  </si>
+  <si>
+    <t>Manoj kumar dubey</t>
+  </si>
+  <si>
+    <t>Sooraj</t>
+  </si>
+  <si>
+    <t>Virendra kumar</t>
+  </si>
+  <si>
+    <t>Siddharth chawla</t>
+  </si>
+  <si>
+    <t>KRISHAN KUMAR</t>
+  </si>
+  <si>
+    <t>Anil kumar</t>
+  </si>
+  <si>
+    <t>Manish Dahiya</t>
+  </si>
+  <si>
+    <t>Raunak kharwar</t>
+  </si>
+  <si>
+    <t>Devender saru</t>
+  </si>
+  <si>
+    <t>Kaushal Kumar</t>
+  </si>
+  <si>
+    <t>Sohan Lal</t>
+  </si>
+  <si>
+    <t>Sukhvind</t>
+  </si>
+  <si>
+    <t>Vivek varma</t>
+  </si>
+  <si>
+    <t>JITENDER</t>
+  </si>
+  <si>
+    <t>RATAN SINGH</t>
+  </si>
+  <si>
+    <t>BHUP SINGH</t>
+  </si>
+  <si>
+    <t>RAMESH</t>
+  </si>
+  <si>
+    <t>Ramdhar</t>
+  </si>
+  <si>
+    <t>Vicky</t>
+  </si>
+  <si>
+    <t>Pinku maurya</t>
+  </si>
+  <si>
+    <t>Pawan Kumar</t>
+  </si>
+  <si>
+    <t>Sushil</t>
+  </si>
+  <si>
+    <t>Vijay</t>
+  </si>
+  <si>
+    <t>Sumit bhargav</t>
+  </si>
+  <si>
+    <t>Vikash Singh</t>
+  </si>
+  <si>
+    <t>Nirmal Kumar</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Aman</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar</t>
+  </si>
+  <si>
+    <t>Vivek Kumar</t>
+  </si>
+  <si>
+    <t>Shashi Kant</t>
+  </si>
+  <si>
+    <t>Akash</t>
+  </si>
+  <si>
+    <t>Arvind kumar</t>
+  </si>
+  <si>
+    <t>Mukesh</t>
+  </si>
+  <si>
+    <t>VIJAY PAL</t>
+  </si>
+  <si>
+    <t>Kallu</t>
+  </si>
+  <si>
+    <t>Ashish Kumar</t>
+  </si>
+  <si>
+    <t>Satayveer</t>
+  </si>
+  <si>
+    <t>Uday</t>
+  </si>
+  <si>
+    <t>Shravan</t>
+  </si>
+  <si>
+    <t>Upendra mishra</t>
+  </si>
+  <si>
+    <t>Santosh Kumar Ray</t>
+  </si>
+  <si>
+    <t>Vicky Das</t>
+  </si>
+  <si>
+    <t>Shailesh Kumar</t>
+  </si>
+  <si>
+    <t>Vikram</t>
+  </si>
+  <si>
+    <t>Gulab Singh</t>
+  </si>
+  <si>
+    <t>Jamuna</t>
+  </si>
+  <si>
+    <t>Mukesh Kumar</t>
+  </si>
+  <si>
+    <t>Ranbeer Kumar</t>
+  </si>
+  <si>
+    <t>Rajendra</t>
+  </si>
+  <si>
+    <t>Vineet Kumar</t>
+  </si>
+  <si>
+    <t>Anurag</t>
+  </si>
+  <si>
+    <t>Sourabh Kumar</t>
+  </si>
+  <si>
+    <t>Dilip Kumar</t>
+  </si>
+  <si>
+    <t>Nandal bauri</t>
+  </si>
+  <si>
+    <t>Niraj Kumar</t>
+  </si>
+  <si>
+    <t>Gautam Kumar</t>
+  </si>
+  <si>
+    <t>Akhilesh</t>
+  </si>
+  <si>
+    <t>CD- Gopalpur</t>
+  </si>
+  <si>
+    <t>30000377478</t>
+  </si>
+  <si>
+    <t>7826379498</t>
+  </si>
+  <si>
+    <t>220912010000510</t>
+  </si>
+  <si>
+    <t>6284556855</t>
+  </si>
+  <si>
+    <t>920010063138757</t>
+  </si>
+  <si>
+    <t>059210286946</t>
+  </si>
+  <si>
+    <t>50100618494460</t>
+  </si>
+  <si>
+    <t>7049793504</t>
+  </si>
+  <si>
+    <t>50100484275742</t>
+  </si>
+  <si>
+    <t>1908101700001545</t>
+  </si>
+  <si>
+    <t>50100406875549</t>
+  </si>
+  <si>
+    <t>50100660212141</t>
+  </si>
+  <si>
+    <t>40007286110</t>
+  </si>
+  <si>
+    <t>059610126137</t>
+  </si>
+  <si>
+    <t>480402010846495</t>
+  </si>
+  <si>
+    <t>30130100016201</t>
+  </si>
+  <si>
+    <t>613040100004575</t>
+  </si>
+  <si>
+    <t>50449360653</t>
+  </si>
+  <si>
+    <t>50800100021282</t>
+  </si>
+  <si>
+    <t>5907101000723</t>
+  </si>
+  <si>
+    <t>82102200132891</t>
+  </si>
+  <si>
+    <t>220910100042003</t>
+  </si>
+  <si>
+    <t>220910100014727</t>
+  </si>
+  <si>
+    <t>50426286574</t>
+  </si>
+  <si>
+    <t>76430100290196</t>
+  </si>
+  <si>
+    <t>061010340092</t>
+  </si>
+  <si>
+    <t>061010184635</t>
+  </si>
+  <si>
+    <t>433502011004480</t>
+  </si>
+  <si>
+    <t>921010037679872</t>
+  </si>
+  <si>
+    <t>0776001700136291</t>
+  </si>
+  <si>
+    <t>058710605701</t>
+  </si>
+  <si>
+    <t>7965000100045610</t>
+  </si>
+  <si>
+    <t>77500100020351</t>
+  </si>
+  <si>
+    <t>65000100005898</t>
+  </si>
+  <si>
+    <t>76320100934327</t>
+  </si>
+  <si>
+    <t>2806001700068174</t>
+  </si>
+  <si>
+    <t>50100615083440</t>
+  </si>
+  <si>
+    <t>924010012515448</t>
+  </si>
+  <si>
+    <t>30001477467</t>
+  </si>
+  <si>
+    <t>925010027544593</t>
+  </si>
+  <si>
+    <t>2151210635061851</t>
+  </si>
+  <si>
+    <t>30308100001933</t>
+  </si>
+  <si>
+    <t>7751636803</t>
+  </si>
+  <si>
+    <t>50100369513100</t>
+  </si>
+  <si>
+    <t>35062308650</t>
+  </si>
+  <si>
+    <t>50100641969338</t>
+  </si>
+  <si>
+    <t>4868000100061970</t>
+  </si>
+  <si>
+    <t>1908101700032608</t>
+  </si>
+  <si>
+    <t>6572001700059709</t>
+  </si>
+  <si>
+    <t>921010037678633</t>
+  </si>
+  <si>
+    <t>921010037679953</t>
+  </si>
+  <si>
+    <t>50100557647243</t>
+  </si>
+  <si>
+    <t>1908101700017520</t>
+  </si>
+  <si>
+    <t>50100474630487</t>
+  </si>
+  <si>
+    <t>921010037680364</t>
+  </si>
+  <si>
+    <t>50100585684681</t>
+  </si>
+  <si>
+    <t>689602010001397</t>
+  </si>
+  <si>
+    <t>304502019012418</t>
+  </si>
+  <si>
+    <t>50100468687461</t>
+  </si>
+  <si>
+    <t>100201814809</t>
+  </si>
+  <si>
+    <t>925010008398498</t>
+  </si>
+  <si>
+    <t>689602120003400</t>
+  </si>
+  <si>
+    <t>925010011758328</t>
+  </si>
+  <si>
+    <t>520101063367064</t>
+  </si>
+  <si>
+    <t>50100656344557</t>
+  </si>
+  <si>
+    <t>76321900878763</t>
+  </si>
+  <si>
+    <t>639002120020609</t>
+  </si>
+  <si>
+    <t>639002120020608</t>
+  </si>
+  <si>
+    <t>925010011758344</t>
+  </si>
+  <si>
+    <t>6937537504</t>
+  </si>
+  <si>
+    <t>102350149963</t>
+  </si>
+  <si>
+    <t>1116717431</t>
+  </si>
+  <si>
+    <t>6937460890</t>
+  </si>
+  <si>
+    <t>6937537489</t>
+  </si>
+  <si>
+    <t>6937537522</t>
+  </si>
+  <si>
+    <t>6937537539</t>
+  </si>
+  <si>
+    <t>6937537386</t>
+  </si>
+  <si>
+    <t>102085754220</t>
+  </si>
+  <si>
+    <t>6937537441</t>
+  </si>
+  <si>
+    <t>102398979624</t>
+  </si>
+  <si>
+    <t>6937537462</t>
+  </si>
+  <si>
+    <t>6937537413</t>
+  </si>
+  <si>
+    <t>102099547345</t>
+  </si>
+  <si>
+    <t>6936170547</t>
+  </si>
+  <si>
+    <t>Helper</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Electrician</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1106,8 +1767,32 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1120,8 +1805,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1144,12 +1841,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1168,12 +1905,96 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1471,11 +2292,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM139"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="8" max="8" width="12.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9148,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="5">
-        <f t="shared" ref="U66:U69" si="5">+ROUND(SUM(Q66:T66),0)</f>
+        <f t="shared" ref="U66:U129" si="5">+ROUND(SUM(Q66:T66),0)</f>
         <v>13281</v>
       </c>
       <c r="V66" s="3">
@@ -9287,7 +10108,7 @@
         <v>0</v>
       </c>
       <c r="AD67" s="5">
-        <f t="shared" ref="AD67:AD69" si="7">+U67+AA67+AB67+AC67+V67+W67+X67+Y67+Z67</f>
+        <f t="shared" ref="AD67:AD130" si="7">+U67+AA67+AB67+AC67+V67+W67+X67+Y67+Z67</f>
         <v>12556</v>
       </c>
       <c r="AE67" s="4">
@@ -9554,7 +10375,6393 @@
         <v>10705</v>
       </c>
     </row>
+    <row r="70" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A70" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G70" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="H70" s="24">
+        <v>0</v>
+      </c>
+      <c r="I70" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="J70" s="12">
+        <v>26</v>
+      </c>
+      <c r="K70">
+        <v>12</v>
+      </c>
+      <c r="L70" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M70" s="29"/>
+      <c r="N70" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P70">
+        <v>16489</v>
+      </c>
+      <c r="Q70">
+        <v>7025</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>585</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70" s="5">
+        <f t="shared" si="5"/>
+        <v>7610</v>
+      </c>
+      <c r="W70" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="5">
+        <f t="shared" si="7"/>
+        <v>7610</v>
+      </c>
+      <c r="AE70">
+        <v>843</v>
+      </c>
+      <c r="AF70">
+        <v>53</v>
+      </c>
+      <c r="AG70">
+        <v>15</v>
+      </c>
+      <c r="AJ70" s="12">
+        <v>3000</v>
+      </c>
+      <c r="AL70" s="5">
+        <f t="shared" ref="AL70:AL133" si="9">+ROUND(AJ70+AI70+AG70+AF70+AE70+AK70,0)+AH70</f>
+        <v>3911</v>
+      </c>
+      <c r="AM70" s="5">
+        <f t="shared" ref="AM70:AM133" si="10">+AD70-AL70</f>
+        <v>3699</v>
+      </c>
+    </row>
+    <row r="71" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A71" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="E71" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G71" s="20" t="s">
+        <v>481</v>
+      </c>
+      <c r="H71" s="25">
+        <v>102117378186</v>
+      </c>
+      <c r="I71" s="25">
+        <v>6934438467</v>
+      </c>
+      <c r="J71" s="12">
+        <v>26</v>
+      </c>
+      <c r="K71">
+        <v>18</v>
+      </c>
+      <c r="L71" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M71" s="29"/>
+      <c r="N71" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P71">
+        <v>16489</v>
+      </c>
+      <c r="Q71">
+        <v>10538</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>878</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71" s="5">
+        <f t="shared" si="5"/>
+        <v>11416</v>
+      </c>
+      <c r="W71" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="5">
+        <f t="shared" si="7"/>
+        <v>11416</v>
+      </c>
+      <c r="AE71">
+        <v>1265</v>
+      </c>
+      <c r="AF71">
+        <v>79</v>
+      </c>
+      <c r="AG71">
+        <v>23</v>
+      </c>
+      <c r="AJ71" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="5">
+        <f t="shared" si="9"/>
+        <v>1367</v>
+      </c>
+      <c r="AM71" s="5">
+        <f t="shared" si="10"/>
+        <v>10049</v>
+      </c>
+    </row>
+    <row r="72" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A72" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="E72" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="H72" s="25">
+        <v>102195780752</v>
+      </c>
+      <c r="I72" s="25">
+        <v>6936026694</v>
+      </c>
+      <c r="J72" s="12">
+        <v>26</v>
+      </c>
+      <c r="K72">
+        <v>18</v>
+      </c>
+      <c r="L72" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M72" s="29"/>
+      <c r="N72" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P72">
+        <v>16489</v>
+      </c>
+      <c r="Q72">
+        <v>10538</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>878</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72" s="5">
+        <f t="shared" si="5"/>
+        <v>11416</v>
+      </c>
+      <c r="W72" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="5">
+        <f t="shared" si="7"/>
+        <v>11416</v>
+      </c>
+      <c r="AE72">
+        <v>1265</v>
+      </c>
+      <c r="AF72">
+        <v>79</v>
+      </c>
+      <c r="AG72">
+        <v>23</v>
+      </c>
+      <c r="AJ72" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="5">
+        <f t="shared" si="9"/>
+        <v>1367</v>
+      </c>
+      <c r="AM72" s="5">
+        <f t="shared" si="10"/>
+        <v>10049</v>
+      </c>
+    </row>
+    <row r="73" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A73" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="E73" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>483</v>
+      </c>
+      <c r="H73" s="25">
+        <v>101633242357</v>
+      </c>
+      <c r="I73" s="25">
+        <v>6935725448</v>
+      </c>
+      <c r="J73" s="12">
+        <v>26</v>
+      </c>
+      <c r="K73">
+        <v>20</v>
+      </c>
+      <c r="L73" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M73" s="29"/>
+      <c r="N73" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P73">
+        <v>16489</v>
+      </c>
+      <c r="Q73">
+        <v>11708</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>975</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73" s="5">
+        <f t="shared" si="5"/>
+        <v>12683</v>
+      </c>
+      <c r="W73" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="5">
+        <f t="shared" si="7"/>
+        <v>12683</v>
+      </c>
+      <c r="AE73">
+        <v>1405</v>
+      </c>
+      <c r="AF73">
+        <v>88</v>
+      </c>
+      <c r="AG73">
+        <v>25</v>
+      </c>
+      <c r="AJ73" s="20">
+        <v>2000</v>
+      </c>
+      <c r="AL73" s="5">
+        <f t="shared" si="9"/>
+        <v>3518</v>
+      </c>
+      <c r="AM73" s="5">
+        <f t="shared" si="10"/>
+        <v>9165</v>
+      </c>
+    </row>
+    <row r="74" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A74" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="E74" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G74" s="20" t="s">
+        <v>484</v>
+      </c>
+      <c r="H74" s="25">
+        <v>101289460566</v>
+      </c>
+      <c r="I74" s="25">
+        <v>1116542310</v>
+      </c>
+      <c r="J74" s="12">
+        <v>26</v>
+      </c>
+      <c r="K74">
+        <v>21</v>
+      </c>
+      <c r="L74" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M74" s="29"/>
+      <c r="N74" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P74">
+        <v>16489</v>
+      </c>
+      <c r="Q74">
+        <v>12294</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>1024</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74" s="5">
+        <f t="shared" si="5"/>
+        <v>13318</v>
+      </c>
+      <c r="W74" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="5">
+        <f t="shared" si="7"/>
+        <v>13318</v>
+      </c>
+      <c r="AE74">
+        <v>1475</v>
+      </c>
+      <c r="AF74">
+        <v>92</v>
+      </c>
+      <c r="AG74">
+        <v>27</v>
+      </c>
+      <c r="AJ74" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="5">
+        <f t="shared" si="9"/>
+        <v>1594</v>
+      </c>
+      <c r="AM74" s="5">
+        <f t="shared" si="10"/>
+        <v>11724</v>
+      </c>
+    </row>
+    <row r="75" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A75" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="E75" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>485</v>
+      </c>
+      <c r="H75" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="I75" s="25" t="s">
+        <v>551</v>
+      </c>
+      <c r="J75" s="12">
+        <v>26</v>
+      </c>
+      <c r="K75">
+        <v>22</v>
+      </c>
+      <c r="L75" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M75" s="29"/>
+      <c r="N75" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P75">
+        <v>16489</v>
+      </c>
+      <c r="Q75">
+        <v>12879</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>1073</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75" s="5">
+        <f t="shared" si="5"/>
+        <v>13952</v>
+      </c>
+      <c r="W75" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="5">
+        <f t="shared" si="7"/>
+        <v>13952</v>
+      </c>
+      <c r="AE75">
+        <v>1546</v>
+      </c>
+      <c r="AF75">
+        <v>97</v>
+      </c>
+      <c r="AG75">
+        <v>28</v>
+      </c>
+      <c r="AJ75" s="12">
+        <v>3000</v>
+      </c>
+      <c r="AL75" s="5">
+        <f t="shared" si="9"/>
+        <v>4671</v>
+      </c>
+      <c r="AM75" s="5">
+        <f t="shared" si="10"/>
+        <v>9281</v>
+      </c>
+    </row>
+    <row r="76" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A76" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="E76" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G76" s="20" t="s">
+        <v>486</v>
+      </c>
+      <c r="H76" s="25">
+        <v>102019864254</v>
+      </c>
+      <c r="I76" s="25">
+        <v>6932878661</v>
+      </c>
+      <c r="J76" s="12">
+        <v>26</v>
+      </c>
+      <c r="K76">
+        <v>25</v>
+      </c>
+      <c r="L76" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M76" s="29"/>
+      <c r="N76" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P76">
+        <v>16489</v>
+      </c>
+      <c r="Q76">
+        <v>14636</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>1219</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W76" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="5">
+        <f t="shared" si="7"/>
+        <v>15855</v>
+      </c>
+      <c r="AE76">
+        <v>1756</v>
+      </c>
+      <c r="AF76">
+        <v>110</v>
+      </c>
+      <c r="AG76">
+        <v>32</v>
+      </c>
+      <c r="AJ76" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="5">
+        <f t="shared" si="9"/>
+        <v>1898</v>
+      </c>
+      <c r="AM76" s="5">
+        <f t="shared" si="10"/>
+        <v>13957</v>
+      </c>
+    </row>
+    <row r="77" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A77" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="E77" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G77" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="H77" s="26">
+        <v>102383758982</v>
+      </c>
+      <c r="I77" s="25">
+        <v>6937460914</v>
+      </c>
+      <c r="J77" s="12">
+        <v>26</v>
+      </c>
+      <c r="K77">
+        <v>25</v>
+      </c>
+      <c r="L77" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M77" s="29"/>
+      <c r="N77" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P77">
+        <v>16489</v>
+      </c>
+      <c r="Q77">
+        <v>14636</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>1219</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W77" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="5">
+        <f t="shared" si="7"/>
+        <v>15855</v>
+      </c>
+      <c r="AE77">
+        <v>1756</v>
+      </c>
+      <c r="AF77">
+        <v>110</v>
+      </c>
+      <c r="AG77">
+        <v>32</v>
+      </c>
+      <c r="AJ77" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="5">
+        <f t="shared" si="9"/>
+        <v>1898</v>
+      </c>
+      <c r="AM77" s="5">
+        <f t="shared" si="10"/>
+        <v>13957</v>
+      </c>
+    </row>
+    <row r="78" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A78" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E78" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F78" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G78" s="20" t="s">
+        <v>488</v>
+      </c>
+      <c r="H78" s="25">
+        <v>101874514872</v>
+      </c>
+      <c r="I78" s="25">
+        <v>6934082961</v>
+      </c>
+      <c r="J78" s="12">
+        <v>26</v>
+      </c>
+      <c r="K78">
+        <v>26</v>
+      </c>
+      <c r="L78" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M78" s="29"/>
+      <c r="N78" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P78">
+        <v>16489</v>
+      </c>
+      <c r="Q78">
+        <v>15221</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>1268</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W78" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB78">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE78">
+        <v>1827</v>
+      </c>
+      <c r="AF78">
+        <v>114</v>
+      </c>
+      <c r="AG78">
+        <v>33</v>
+      </c>
+      <c r="AJ78" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM78" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="79" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A79" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E79" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F79" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G79" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="H79" s="25">
+        <v>101903116884</v>
+      </c>
+      <c r="I79" s="25">
+        <v>2019693390</v>
+      </c>
+      <c r="J79" s="12">
+        <v>26</v>
+      </c>
+      <c r="K79">
+        <v>26</v>
+      </c>
+      <c r="L79" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M79" s="29"/>
+      <c r="N79" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P79">
+        <v>16489</v>
+      </c>
+      <c r="Q79">
+        <v>15221</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>1268</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W79" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB79">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE79">
+        <v>1827</v>
+      </c>
+      <c r="AF79">
+        <v>114</v>
+      </c>
+      <c r="AG79">
+        <v>33</v>
+      </c>
+      <c r="AJ79" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL79" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM79" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="80" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A80" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="E80" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G80" s="20" t="s">
+        <v>490</v>
+      </c>
+      <c r="H80" s="25">
+        <v>100586492370</v>
+      </c>
+      <c r="I80" s="25">
+        <v>6937366315</v>
+      </c>
+      <c r="J80" s="12">
+        <v>26</v>
+      </c>
+      <c r="K80">
+        <v>26</v>
+      </c>
+      <c r="L80" s="28">
+        <v>18500</v>
+      </c>
+      <c r="M80" s="29">
+        <v>8000</v>
+      </c>
+      <c r="N80" s="29">
+        <v>1541</v>
+      </c>
+      <c r="O80" s="29">
+        <v>1067</v>
+      </c>
+      <c r="P80">
+        <v>29108</v>
+      </c>
+      <c r="Q80">
+        <v>18500</v>
+      </c>
+      <c r="R80">
+        <v>8000</v>
+      </c>
+      <c r="S80">
+        <v>1541</v>
+      </c>
+      <c r="T80">
+        <v>1067</v>
+      </c>
+      <c r="U80" s="5">
+        <f t="shared" si="5"/>
+        <v>29108</v>
+      </c>
+      <c r="W80" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB80">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="5">
+        <f t="shared" si="7"/>
+        <v>29808</v>
+      </c>
+      <c r="AE80">
+        <v>2220</v>
+      </c>
+      <c r="AF80">
+        <v>139</v>
+      </c>
+      <c r="AG80">
+        <v>35</v>
+      </c>
+      <c r="AJ80" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL80" s="5">
+        <f t="shared" si="9"/>
+        <v>2394</v>
+      </c>
+      <c r="AM80" s="5">
+        <f t="shared" si="10"/>
+        <v>27414</v>
+      </c>
+    </row>
+    <row r="81" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A81" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="B81" t="s">
+        <v>2</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="E81" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G81" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="H81" s="25">
+        <v>101997205824</v>
+      </c>
+      <c r="I81" s="25">
+        <v>2019693375</v>
+      </c>
+      <c r="J81" s="12">
+        <v>26</v>
+      </c>
+      <c r="K81">
+        <v>26</v>
+      </c>
+      <c r="L81" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M81" s="29"/>
+      <c r="N81" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P81">
+        <v>16489</v>
+      </c>
+      <c r="Q81">
+        <v>15221</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>1268</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W81" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB81">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE81">
+        <v>1827</v>
+      </c>
+      <c r="AF81">
+        <v>114</v>
+      </c>
+      <c r="AG81">
+        <v>33</v>
+      </c>
+      <c r="AJ81" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM81" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="82" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A82" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B82" t="s">
+        <v>2</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="E82" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G82" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="H82" s="25">
+        <v>100480619575</v>
+      </c>
+      <c r="I82" s="25">
+        <v>6933964921</v>
+      </c>
+      <c r="J82" s="12">
+        <v>26</v>
+      </c>
+      <c r="K82">
+        <v>26</v>
+      </c>
+      <c r="L82" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M82" s="29"/>
+      <c r="N82" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P82">
+        <v>16489</v>
+      </c>
+      <c r="Q82">
+        <v>15221</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>1268</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="U82" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W82" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB82">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE82">
+        <v>1827</v>
+      </c>
+      <c r="AF82">
+        <v>114</v>
+      </c>
+      <c r="AG82">
+        <v>33</v>
+      </c>
+      <c r="AJ82" s="20">
+        <v>2000</v>
+      </c>
+      <c r="AL82" s="5">
+        <f t="shared" si="9"/>
+        <v>3974</v>
+      </c>
+      <c r="AM82" s="5">
+        <f t="shared" si="10"/>
+        <v>13215</v>
+      </c>
+    </row>
+    <row r="83" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A83" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E83" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G83" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="H83" s="25">
+        <v>101987052488</v>
+      </c>
+      <c r="I83" s="25">
+        <v>2019770224</v>
+      </c>
+      <c r="J83" s="12">
+        <v>26</v>
+      </c>
+      <c r="K83">
+        <v>26</v>
+      </c>
+      <c r="L83" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M83" s="29"/>
+      <c r="N83" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P83">
+        <v>16489</v>
+      </c>
+      <c r="Q83">
+        <v>15221</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>1268</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W83" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB83">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE83">
+        <v>1827</v>
+      </c>
+      <c r="AF83">
+        <v>114</v>
+      </c>
+      <c r="AG83">
+        <v>33</v>
+      </c>
+      <c r="AJ83" s="20">
+        <v>2000</v>
+      </c>
+      <c r="AL83" s="5">
+        <f t="shared" si="9"/>
+        <v>3974</v>
+      </c>
+      <c r="AM83" s="5">
+        <f t="shared" si="10"/>
+        <v>13215</v>
+      </c>
+    </row>
+    <row r="84" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A84" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B84" t="s">
+        <v>2</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="E84" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G84" s="20" t="s">
+        <v>494</v>
+      </c>
+      <c r="H84" s="25">
+        <v>102208473041</v>
+      </c>
+      <c r="I84" s="25">
+        <v>2019716870</v>
+      </c>
+      <c r="J84" s="12">
+        <v>26</v>
+      </c>
+      <c r="K84">
+        <v>26</v>
+      </c>
+      <c r="L84" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M84" s="29"/>
+      <c r="N84" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P84">
+        <v>16489</v>
+      </c>
+      <c r="Q84">
+        <v>15221</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>1268</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W84" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB84">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE84">
+        <v>1827</v>
+      </c>
+      <c r="AF84">
+        <v>114</v>
+      </c>
+      <c r="AG84">
+        <v>33</v>
+      </c>
+      <c r="AJ84" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM84" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="85" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A85" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B85" t="s">
+        <v>2</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="E85" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F85" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>495</v>
+      </c>
+      <c r="H85" s="24">
+        <v>0</v>
+      </c>
+      <c r="I85" s="25" t="s">
+        <v>552</v>
+      </c>
+      <c r="J85" s="12">
+        <v>26</v>
+      </c>
+      <c r="K85">
+        <v>26</v>
+      </c>
+      <c r="L85" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M85" s="29"/>
+      <c r="N85" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P85">
+        <v>16489</v>
+      </c>
+      <c r="Q85">
+        <v>15221</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>1268</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W85" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB85">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE85">
+        <v>1827</v>
+      </c>
+      <c r="AF85">
+        <v>114</v>
+      </c>
+      <c r="AG85">
+        <v>33</v>
+      </c>
+      <c r="AJ85" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM85" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="86" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A86" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="E86" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G86" s="21" t="s">
+        <v>485</v>
+      </c>
+      <c r="H86" s="24">
+        <v>0</v>
+      </c>
+      <c r="I86" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="J86" s="12">
+        <v>26</v>
+      </c>
+      <c r="K86">
+        <v>26</v>
+      </c>
+      <c r="L86" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M86" s="29"/>
+      <c r="N86" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P86">
+        <v>16489</v>
+      </c>
+      <c r="Q86">
+        <v>15221</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>1268</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W86" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB86">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE86">
+        <v>1827</v>
+      </c>
+      <c r="AF86">
+        <v>114</v>
+      </c>
+      <c r="AG86">
+        <v>33</v>
+      </c>
+      <c r="AJ86" s="12">
+        <v>3000</v>
+      </c>
+      <c r="AL86" s="5">
+        <f t="shared" si="9"/>
+        <v>4974</v>
+      </c>
+      <c r="AM86" s="5">
+        <f t="shared" si="10"/>
+        <v>12215</v>
+      </c>
+    </row>
+    <row r="87" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A87" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="B87" t="s">
+        <v>2</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="E87" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F87" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G87" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="H87" s="24">
+        <v>0</v>
+      </c>
+      <c r="I87" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="J87" s="12">
+        <v>26</v>
+      </c>
+      <c r="K87">
+        <v>26</v>
+      </c>
+      <c r="L87" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M87" s="29"/>
+      <c r="N87" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P87">
+        <v>16489</v>
+      </c>
+      <c r="Q87">
+        <v>15221</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>1268</v>
+      </c>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W87" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB87">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE87">
+        <v>1827</v>
+      </c>
+      <c r="AF87">
+        <v>114</v>
+      </c>
+      <c r="AG87">
+        <v>33</v>
+      </c>
+      <c r="AJ87" s="20">
+        <v>2000</v>
+      </c>
+      <c r="AL87" s="5">
+        <f t="shared" si="9"/>
+        <v>3974</v>
+      </c>
+      <c r="AM87" s="5">
+        <f t="shared" si="10"/>
+        <v>13215</v>
+      </c>
+    </row>
+    <row r="88" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A88" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="E88" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F88" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G88" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="H88" s="24">
+        <v>0</v>
+      </c>
+      <c r="I88" s="25" t="s">
+        <v>555</v>
+      </c>
+      <c r="J88" s="12">
+        <v>26</v>
+      </c>
+      <c r="K88">
+        <v>26</v>
+      </c>
+      <c r="L88" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M88" s="29"/>
+      <c r="N88" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P88">
+        <v>16489</v>
+      </c>
+      <c r="Q88">
+        <v>15221</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>1268</v>
+      </c>
+      <c r="T88">
+        <v>0</v>
+      </c>
+      <c r="U88" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W88" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB88">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE88">
+        <v>1827</v>
+      </c>
+      <c r="AF88">
+        <v>114</v>
+      </c>
+      <c r="AG88">
+        <v>33</v>
+      </c>
+      <c r="AJ88" s="20">
+        <v>2000</v>
+      </c>
+      <c r="AL88" s="5">
+        <f t="shared" si="9"/>
+        <v>3974</v>
+      </c>
+      <c r="AM88" s="5">
+        <f t="shared" si="10"/>
+        <v>13215</v>
+      </c>
+    </row>
+    <row r="89" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A89" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="B89" t="s">
+        <v>2</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="E89" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F89" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G89" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="H89" s="27">
+        <v>102152100225</v>
+      </c>
+      <c r="I89" s="25">
+        <v>2019693397</v>
+      </c>
+      <c r="J89" s="12">
+        <v>26</v>
+      </c>
+      <c r="K89">
+        <v>17</v>
+      </c>
+      <c r="L89" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M89" s="29"/>
+      <c r="N89" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P89">
+        <v>16489</v>
+      </c>
+      <c r="Q89">
+        <v>9952</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>829</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89" s="5">
+        <f t="shared" si="5"/>
+        <v>10781</v>
+      </c>
+      <c r="W89" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB89">
+        <v>1962</v>
+      </c>
+      <c r="AD89" s="5">
+        <f t="shared" si="7"/>
+        <v>12743</v>
+      </c>
+      <c r="AE89">
+        <v>1194</v>
+      </c>
+      <c r="AF89">
+        <v>75</v>
+      </c>
+      <c r="AG89">
+        <v>22</v>
+      </c>
+      <c r="AJ89" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="5">
+        <f t="shared" si="9"/>
+        <v>1291</v>
+      </c>
+      <c r="AM89" s="5">
+        <f t="shared" si="10"/>
+        <v>11452</v>
+      </c>
+    </row>
+    <row r="90" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A90" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="B90" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="E90" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F90" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G90" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="H90" s="25">
+        <v>101010197111</v>
+      </c>
+      <c r="I90" s="25">
+        <v>6935387745</v>
+      </c>
+      <c r="J90" s="12">
+        <v>26</v>
+      </c>
+      <c r="K90">
+        <v>25</v>
+      </c>
+      <c r="L90" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M90" s="29"/>
+      <c r="N90" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P90">
+        <v>16489</v>
+      </c>
+      <c r="Q90">
+        <v>14636</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>1219</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W90" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB90">
+        <v>962</v>
+      </c>
+      <c r="AD90" s="5">
+        <f t="shared" si="7"/>
+        <v>16817</v>
+      </c>
+      <c r="AE90">
+        <v>1756</v>
+      </c>
+      <c r="AF90">
+        <v>110</v>
+      </c>
+      <c r="AG90">
+        <v>32</v>
+      </c>
+      <c r="AJ90" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="5">
+        <f t="shared" si="9"/>
+        <v>1898</v>
+      </c>
+      <c r="AM90" s="5">
+        <f t="shared" si="10"/>
+        <v>14919</v>
+      </c>
+    </row>
+    <row r="91" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A91" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B91" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="E91" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F91" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G91" s="20" t="s">
+        <v>500</v>
+      </c>
+      <c r="H91" s="25">
+        <v>101700989072</v>
+      </c>
+      <c r="I91" s="25">
+        <v>2019693389</v>
+      </c>
+      <c r="J91" s="12">
+        <v>26</v>
+      </c>
+      <c r="K91">
+        <v>26</v>
+      </c>
+      <c r="L91" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M91" s="29"/>
+      <c r="N91" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P91">
+        <v>16489</v>
+      </c>
+      <c r="Q91">
+        <v>15221</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>1268</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="U91" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W91" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB91">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE91">
+        <v>1827</v>
+      </c>
+      <c r="AF91">
+        <v>114</v>
+      </c>
+      <c r="AG91">
+        <v>33</v>
+      </c>
+      <c r="AJ91" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM91" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="92" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A92" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="B92" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="E92" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F92" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G92" s="20" t="s">
+        <v>501</v>
+      </c>
+      <c r="H92" s="25">
+        <v>101194770011</v>
+      </c>
+      <c r="I92" s="25">
+        <v>6932968973</v>
+      </c>
+      <c r="J92" s="12">
+        <v>26</v>
+      </c>
+      <c r="K92">
+        <v>26</v>
+      </c>
+      <c r="L92" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M92" s="29"/>
+      <c r="N92" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P92">
+        <v>16489</v>
+      </c>
+      <c r="Q92">
+        <v>15221</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+      <c r="S92">
+        <v>1268</v>
+      </c>
+      <c r="T92">
+        <v>0</v>
+      </c>
+      <c r="U92" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W92" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB92">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE92">
+        <v>1827</v>
+      </c>
+      <c r="AF92">
+        <v>114</v>
+      </c>
+      <c r="AG92">
+        <v>33</v>
+      </c>
+      <c r="AJ92" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM92" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="93" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A93" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="B93" t="s">
+        <v>2</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="E93" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G93" s="20" t="s">
+        <v>502</v>
+      </c>
+      <c r="H93" s="25">
+        <v>101995548803</v>
+      </c>
+      <c r="I93" s="25">
+        <v>6933984611</v>
+      </c>
+      <c r="J93" s="12">
+        <v>26</v>
+      </c>
+      <c r="K93">
+        <v>26</v>
+      </c>
+      <c r="L93" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M93" s="29"/>
+      <c r="N93" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P93">
+        <v>16489</v>
+      </c>
+      <c r="Q93">
+        <v>15221</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+      <c r="S93">
+        <v>1268</v>
+      </c>
+      <c r="T93">
+        <v>0</v>
+      </c>
+      <c r="U93" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W93" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB93">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE93">
+        <v>1827</v>
+      </c>
+      <c r="AF93">
+        <v>114</v>
+      </c>
+      <c r="AG93">
+        <v>33</v>
+      </c>
+      <c r="AJ93" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM93" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="94" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A94" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B94" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="E94" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="F94" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G94" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="H94" s="24">
+        <v>0</v>
+      </c>
+      <c r="I94" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="J94" s="12">
+        <v>26</v>
+      </c>
+      <c r="K94">
+        <v>26</v>
+      </c>
+      <c r="L94" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M94" s="29"/>
+      <c r="N94" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P94">
+        <v>16489</v>
+      </c>
+      <c r="Q94">
+        <v>15221</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+      <c r="S94">
+        <v>1268</v>
+      </c>
+      <c r="T94">
+        <v>0</v>
+      </c>
+      <c r="U94" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W94" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB94">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE94">
+        <v>1827</v>
+      </c>
+      <c r="AF94">
+        <v>114</v>
+      </c>
+      <c r="AG94">
+        <v>33</v>
+      </c>
+      <c r="AJ94" s="20">
+        <v>2000</v>
+      </c>
+      <c r="AL94" s="5">
+        <f t="shared" si="9"/>
+        <v>3974</v>
+      </c>
+      <c r="AM94" s="5">
+        <f t="shared" si="10"/>
+        <v>13215</v>
+      </c>
+    </row>
+    <row r="95" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A95" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="B95" t="s">
+        <v>2</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E95" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F95" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G95" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="H95" s="25">
+        <v>101700989126</v>
+      </c>
+      <c r="I95" s="26">
+        <v>6933908645</v>
+      </c>
+      <c r="J95" s="12">
+        <v>26</v>
+      </c>
+      <c r="K95">
+        <v>4</v>
+      </c>
+      <c r="L95" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M95" s="29"/>
+      <c r="N95" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P95">
+        <v>16489</v>
+      </c>
+      <c r="Q95">
+        <v>2342</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <v>195</v>
+      </c>
+      <c r="T95">
+        <v>0</v>
+      </c>
+      <c r="U95" s="5">
+        <f t="shared" si="5"/>
+        <v>2537</v>
+      </c>
+      <c r="W95" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB95">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="5">
+        <f t="shared" si="7"/>
+        <v>2537</v>
+      </c>
+      <c r="AE95">
+        <v>281</v>
+      </c>
+      <c r="AF95">
+        <v>18</v>
+      </c>
+      <c r="AG95">
+        <v>5</v>
+      </c>
+      <c r="AJ95" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL95" s="5">
+        <f t="shared" si="9"/>
+        <v>304</v>
+      </c>
+      <c r="AM95" s="5">
+        <f t="shared" si="10"/>
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="96" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A96" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="B96" t="s">
+        <v>2</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="E96" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G96" s="20" t="s">
+        <v>505</v>
+      </c>
+      <c r="H96" s="25">
+        <v>102300407720</v>
+      </c>
+      <c r="I96" s="26">
+        <v>6725450846</v>
+      </c>
+      <c r="J96" s="12">
+        <v>26</v>
+      </c>
+      <c r="K96">
+        <v>4</v>
+      </c>
+      <c r="L96" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M96" s="29"/>
+      <c r="N96" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P96">
+        <v>16489</v>
+      </c>
+      <c r="Q96">
+        <v>2342</v>
+      </c>
+      <c r="R96">
+        <v>0</v>
+      </c>
+      <c r="S96">
+        <v>195</v>
+      </c>
+      <c r="T96">
+        <v>0</v>
+      </c>
+      <c r="U96" s="5">
+        <f t="shared" si="5"/>
+        <v>2537</v>
+      </c>
+      <c r="W96" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB96">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="5">
+        <f t="shared" si="7"/>
+        <v>2537</v>
+      </c>
+      <c r="AE96">
+        <v>281</v>
+      </c>
+      <c r="AF96">
+        <v>18</v>
+      </c>
+      <c r="AG96">
+        <v>5</v>
+      </c>
+      <c r="AJ96" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="5">
+        <f t="shared" si="9"/>
+        <v>304</v>
+      </c>
+      <c r="AM96" s="5">
+        <f t="shared" si="10"/>
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="97" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A97" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B97" t="s">
+        <v>2</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="E97" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F97" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G97" s="20" t="s">
+        <v>506</v>
+      </c>
+      <c r="H97" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="I97" s="25" t="s">
+        <v>558</v>
+      </c>
+      <c r="J97" s="12">
+        <v>26</v>
+      </c>
+      <c r="K97">
+        <v>9</v>
+      </c>
+      <c r="L97" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M97" s="29"/>
+      <c r="N97" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P97">
+        <v>16489</v>
+      </c>
+      <c r="Q97">
+        <v>5269</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <v>439</v>
+      </c>
+      <c r="T97">
+        <v>0</v>
+      </c>
+      <c r="U97" s="5">
+        <f t="shared" si="5"/>
+        <v>5708</v>
+      </c>
+      <c r="W97" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB97">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="5">
+        <f t="shared" si="7"/>
+        <v>5708</v>
+      </c>
+      <c r="AE97">
+        <v>632</v>
+      </c>
+      <c r="AF97">
+        <v>40</v>
+      </c>
+      <c r="AG97">
+        <v>11</v>
+      </c>
+      <c r="AJ97" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="5">
+        <f t="shared" si="9"/>
+        <v>683</v>
+      </c>
+      <c r="AM97" s="5">
+        <f t="shared" si="10"/>
+        <v>5025</v>
+      </c>
+    </row>
+    <row r="98" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A98" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B98" t="s">
+        <v>2</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="E98" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G98" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="H98" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="I98" s="25" t="s">
+        <v>560</v>
+      </c>
+      <c r="J98" s="12">
+        <v>26</v>
+      </c>
+      <c r="K98">
+        <v>10</v>
+      </c>
+      <c r="L98" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M98" s="29"/>
+      <c r="N98" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P98">
+        <v>16489</v>
+      </c>
+      <c r="Q98">
+        <v>5854</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+      <c r="S98">
+        <v>488</v>
+      </c>
+      <c r="T98">
+        <v>0</v>
+      </c>
+      <c r="U98" s="5">
+        <f t="shared" si="5"/>
+        <v>6342</v>
+      </c>
+      <c r="W98" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB98">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="5">
+        <f t="shared" si="7"/>
+        <v>6342</v>
+      </c>
+      <c r="AE98">
+        <v>703</v>
+      </c>
+      <c r="AF98">
+        <v>44</v>
+      </c>
+      <c r="AG98">
+        <v>13</v>
+      </c>
+      <c r="AJ98" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="5">
+        <f t="shared" si="9"/>
+        <v>760</v>
+      </c>
+      <c r="AM98" s="5">
+        <f t="shared" si="10"/>
+        <v>5582</v>
+      </c>
+    </row>
+    <row r="99" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A99" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="B99" t="s">
+        <v>2</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="E99" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F99" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G99" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="H99" s="25">
+        <v>102009182148</v>
+      </c>
+      <c r="I99" s="25">
+        <v>6934120577</v>
+      </c>
+      <c r="J99" s="12">
+        <v>26</v>
+      </c>
+      <c r="K99">
+        <v>11</v>
+      </c>
+      <c r="L99" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M99" s="29"/>
+      <c r="N99" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P99">
+        <v>16489</v>
+      </c>
+      <c r="Q99">
+        <v>6440</v>
+      </c>
+      <c r="R99">
+        <v>0</v>
+      </c>
+      <c r="S99">
+        <v>536</v>
+      </c>
+      <c r="T99">
+        <v>0</v>
+      </c>
+      <c r="U99" s="5">
+        <f t="shared" si="5"/>
+        <v>6976</v>
+      </c>
+      <c r="W99" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB99">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="5">
+        <f t="shared" si="7"/>
+        <v>6976</v>
+      </c>
+      <c r="AE99">
+        <v>773</v>
+      </c>
+      <c r="AF99">
+        <v>48</v>
+      </c>
+      <c r="AG99">
+        <v>14</v>
+      </c>
+      <c r="AJ99" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="5">
+        <f t="shared" si="9"/>
+        <v>835</v>
+      </c>
+      <c r="AM99" s="5">
+        <f t="shared" si="10"/>
+        <v>6141</v>
+      </c>
+    </row>
+    <row r="100" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A100" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="B100" t="s">
+        <v>2</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="E100" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F100" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G100" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="H100" s="25">
+        <v>102370307654</v>
+      </c>
+      <c r="I100" s="26">
+        <v>6937392004</v>
+      </c>
+      <c r="J100" s="12">
+        <v>26</v>
+      </c>
+      <c r="K100">
+        <v>14</v>
+      </c>
+      <c r="L100" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M100" s="29"/>
+      <c r="N100" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P100">
+        <v>16489</v>
+      </c>
+      <c r="Q100">
+        <v>8196</v>
+      </c>
+      <c r="R100">
+        <v>0</v>
+      </c>
+      <c r="S100">
+        <v>683</v>
+      </c>
+      <c r="T100">
+        <v>0</v>
+      </c>
+      <c r="U100" s="5">
+        <f t="shared" si="5"/>
+        <v>8879</v>
+      </c>
+      <c r="W100" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB100">
+        <v>585</v>
+      </c>
+      <c r="AD100" s="5">
+        <f t="shared" si="7"/>
+        <v>9464</v>
+      </c>
+      <c r="AE100">
+        <v>984</v>
+      </c>
+      <c r="AF100">
+        <v>61</v>
+      </c>
+      <c r="AG100">
+        <v>18</v>
+      </c>
+      <c r="AJ100" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="5">
+        <f t="shared" si="9"/>
+        <v>1063</v>
+      </c>
+      <c r="AM100" s="5">
+        <f t="shared" si="10"/>
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="101" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A101" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="B101" t="s">
+        <v>2</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="E101" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F101" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G101" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="H101" s="25">
+        <v>102185126672</v>
+      </c>
+      <c r="I101" s="25">
+        <v>6935976414</v>
+      </c>
+      <c r="J101" s="12">
+        <v>26</v>
+      </c>
+      <c r="K101">
+        <v>17</v>
+      </c>
+      <c r="L101" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M101" s="29"/>
+      <c r="N101" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P101">
+        <v>16489</v>
+      </c>
+      <c r="Q101">
+        <v>9952</v>
+      </c>
+      <c r="R101">
+        <v>0</v>
+      </c>
+      <c r="S101">
+        <v>829</v>
+      </c>
+      <c r="T101">
+        <v>0</v>
+      </c>
+      <c r="U101" s="5">
+        <f t="shared" si="5"/>
+        <v>10781</v>
+      </c>
+      <c r="W101" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB101">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="5">
+        <f t="shared" si="7"/>
+        <v>10781</v>
+      </c>
+      <c r="AE101">
+        <v>1194</v>
+      </c>
+      <c r="AF101">
+        <v>75</v>
+      </c>
+      <c r="AG101">
+        <v>22</v>
+      </c>
+      <c r="AJ101" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="5">
+        <f t="shared" si="9"/>
+        <v>1291</v>
+      </c>
+      <c r="AM101" s="5">
+        <f t="shared" si="10"/>
+        <v>9490</v>
+      </c>
+    </row>
+    <row r="102" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A102" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="B102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="E102" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F102" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G102" s="20" t="s">
+        <v>511</v>
+      </c>
+      <c r="H102" s="25">
+        <v>102370217139</v>
+      </c>
+      <c r="I102" s="26">
+        <v>6937391997</v>
+      </c>
+      <c r="J102" s="12">
+        <v>26</v>
+      </c>
+      <c r="K102">
+        <v>18</v>
+      </c>
+      <c r="L102" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M102" s="29"/>
+      <c r="N102" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P102">
+        <v>16489</v>
+      </c>
+      <c r="Q102">
+        <v>10538</v>
+      </c>
+      <c r="R102">
+        <v>0</v>
+      </c>
+      <c r="S102">
+        <v>878</v>
+      </c>
+      <c r="T102">
+        <v>0</v>
+      </c>
+      <c r="U102" s="5">
+        <f t="shared" si="5"/>
+        <v>11416</v>
+      </c>
+      <c r="W102" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB102">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="5">
+        <f t="shared" si="7"/>
+        <v>11416</v>
+      </c>
+      <c r="AE102">
+        <v>1265</v>
+      </c>
+      <c r="AF102">
+        <v>79</v>
+      </c>
+      <c r="AG102">
+        <v>23</v>
+      </c>
+      <c r="AJ102" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="5">
+        <f t="shared" si="9"/>
+        <v>1367</v>
+      </c>
+      <c r="AM102" s="5">
+        <f t="shared" si="10"/>
+        <v>10049</v>
+      </c>
+    </row>
+    <row r="103" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A103" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="B103" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="E103" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F103" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G103" s="20" t="s">
+        <v>512</v>
+      </c>
+      <c r="H103" s="24">
+        <v>0</v>
+      </c>
+      <c r="I103" s="25" t="s">
+        <v>561</v>
+      </c>
+      <c r="J103" s="12">
+        <v>26</v>
+      </c>
+      <c r="K103">
+        <v>18</v>
+      </c>
+      <c r="L103" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M103" s="29"/>
+      <c r="N103" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P103">
+        <v>16489</v>
+      </c>
+      <c r="Q103">
+        <v>10538</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+      <c r="S103">
+        <v>878</v>
+      </c>
+      <c r="T103">
+        <v>0</v>
+      </c>
+      <c r="U103" s="5">
+        <f t="shared" si="5"/>
+        <v>11416</v>
+      </c>
+      <c r="W103" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB103">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="5">
+        <f t="shared" si="7"/>
+        <v>11416</v>
+      </c>
+      <c r="AE103">
+        <v>1265</v>
+      </c>
+      <c r="AF103">
+        <v>79</v>
+      </c>
+      <c r="AG103">
+        <v>23</v>
+      </c>
+      <c r="AJ103" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL103" s="5">
+        <f t="shared" si="9"/>
+        <v>1367</v>
+      </c>
+      <c r="AM103" s="5">
+        <f t="shared" si="10"/>
+        <v>10049</v>
+      </c>
+    </row>
+    <row r="104" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A104" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B104" t="s">
+        <v>2</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="E104" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G104" s="20" t="s">
+        <v>513</v>
+      </c>
+      <c r="H104" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="I104" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="J104" s="12">
+        <v>26</v>
+      </c>
+      <c r="K104">
+        <v>19</v>
+      </c>
+      <c r="L104" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M104" s="29"/>
+      <c r="N104" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P104">
+        <v>16489</v>
+      </c>
+      <c r="Q104">
+        <v>11123</v>
+      </c>
+      <c r="R104">
+        <v>0</v>
+      </c>
+      <c r="S104">
+        <v>927</v>
+      </c>
+      <c r="T104">
+        <v>0</v>
+      </c>
+      <c r="U104" s="5">
+        <f t="shared" si="5"/>
+        <v>12050</v>
+      </c>
+      <c r="W104" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB104">
+        <v>0</v>
+      </c>
+      <c r="AD104" s="5">
+        <f t="shared" si="7"/>
+        <v>12050</v>
+      </c>
+      <c r="AE104">
+        <v>1335</v>
+      </c>
+      <c r="AF104">
+        <v>83</v>
+      </c>
+      <c r="AG104">
+        <v>24</v>
+      </c>
+      <c r="AJ104" s="20">
+        <v>1500</v>
+      </c>
+      <c r="AL104" s="5">
+        <f t="shared" si="9"/>
+        <v>2942</v>
+      </c>
+      <c r="AM104" s="5">
+        <f t="shared" si="10"/>
+        <v>9108</v>
+      </c>
+    </row>
+    <row r="105" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A105" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="B105" t="s">
+        <v>2</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="E105" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F105" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G105" s="20" t="s">
+        <v>514</v>
+      </c>
+      <c r="H105" s="25">
+        <v>101308873677</v>
+      </c>
+      <c r="I105" s="25">
+        <v>6934868850</v>
+      </c>
+      <c r="J105" s="12">
+        <v>26</v>
+      </c>
+      <c r="K105">
+        <v>21</v>
+      </c>
+      <c r="L105" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M105" s="29"/>
+      <c r="N105" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P105">
+        <v>16489</v>
+      </c>
+      <c r="Q105">
+        <v>12294</v>
+      </c>
+      <c r="R105">
+        <v>0</v>
+      </c>
+      <c r="S105">
+        <v>1024</v>
+      </c>
+      <c r="T105">
+        <v>0</v>
+      </c>
+      <c r="U105" s="5">
+        <f t="shared" si="5"/>
+        <v>13318</v>
+      </c>
+      <c r="W105" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB105">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="5">
+        <f t="shared" si="7"/>
+        <v>13318</v>
+      </c>
+      <c r="AE105">
+        <v>1475</v>
+      </c>
+      <c r="AF105">
+        <v>92</v>
+      </c>
+      <c r="AG105">
+        <v>27</v>
+      </c>
+      <c r="AJ105" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL105" s="5">
+        <f t="shared" si="9"/>
+        <v>1594</v>
+      </c>
+      <c r="AM105" s="5">
+        <f t="shared" si="10"/>
+        <v>11724</v>
+      </c>
+    </row>
+    <row r="106" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A106" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B106" t="s">
+        <v>2</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="E106" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F106" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G106" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="H106" s="25">
+        <v>102220163156</v>
+      </c>
+      <c r="I106" s="25">
+        <v>2019832949</v>
+      </c>
+      <c r="J106" s="12">
+        <v>26</v>
+      </c>
+      <c r="K106">
+        <v>21</v>
+      </c>
+      <c r="L106" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M106" s="29"/>
+      <c r="N106" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P106">
+        <v>16489</v>
+      </c>
+      <c r="Q106">
+        <v>12294</v>
+      </c>
+      <c r="R106">
+        <v>0</v>
+      </c>
+      <c r="S106">
+        <v>1024</v>
+      </c>
+      <c r="T106">
+        <v>0</v>
+      </c>
+      <c r="U106" s="5">
+        <f t="shared" si="5"/>
+        <v>13318</v>
+      </c>
+      <c r="W106" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB106">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="5">
+        <f t="shared" si="7"/>
+        <v>13318</v>
+      </c>
+      <c r="AE106">
+        <v>1475</v>
+      </c>
+      <c r="AF106">
+        <v>92</v>
+      </c>
+      <c r="AG106">
+        <v>27</v>
+      </c>
+      <c r="AJ106" s="12">
+        <v>2000</v>
+      </c>
+      <c r="AL106" s="5">
+        <f t="shared" si="9"/>
+        <v>3594</v>
+      </c>
+      <c r="AM106" s="5">
+        <f t="shared" si="10"/>
+        <v>9724</v>
+      </c>
+    </row>
+    <row r="107" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A107" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="B107" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="E107" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F107" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G107" s="20" t="s">
+        <v>516</v>
+      </c>
+      <c r="H107" s="25">
+        <v>101943641168</v>
+      </c>
+      <c r="I107" s="25">
+        <v>2019693393</v>
+      </c>
+      <c r="J107" s="12">
+        <v>26</v>
+      </c>
+      <c r="K107">
+        <v>22</v>
+      </c>
+      <c r="L107" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M107" s="29"/>
+      <c r="N107" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P107">
+        <v>16489</v>
+      </c>
+      <c r="Q107">
+        <v>12879</v>
+      </c>
+      <c r="R107">
+        <v>0</v>
+      </c>
+      <c r="S107">
+        <v>1073</v>
+      </c>
+      <c r="T107">
+        <v>0</v>
+      </c>
+      <c r="U107" s="5">
+        <f t="shared" si="5"/>
+        <v>13952</v>
+      </c>
+      <c r="W107" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB107">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="5">
+        <f t="shared" si="7"/>
+        <v>13952</v>
+      </c>
+      <c r="AE107">
+        <v>1546</v>
+      </c>
+      <c r="AF107">
+        <v>97</v>
+      </c>
+      <c r="AG107">
+        <v>28</v>
+      </c>
+      <c r="AJ107" s="20">
+        <v>2000</v>
+      </c>
+      <c r="AL107" s="5">
+        <f t="shared" si="9"/>
+        <v>3671</v>
+      </c>
+      <c r="AM107" s="5">
+        <f t="shared" si="10"/>
+        <v>10281</v>
+      </c>
+    </row>
+    <row r="108" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A108" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="B108" t="s">
+        <v>2</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="E108" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F108" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G108" s="20" t="s">
+        <v>517</v>
+      </c>
+      <c r="H108" s="25">
+        <v>102094137829</v>
+      </c>
+      <c r="I108" s="25">
+        <v>6935386393</v>
+      </c>
+      <c r="J108" s="12">
+        <v>26</v>
+      </c>
+      <c r="K108">
+        <v>22</v>
+      </c>
+      <c r="L108" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M108" s="29"/>
+      <c r="N108" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P108">
+        <v>16489</v>
+      </c>
+      <c r="Q108">
+        <v>12879</v>
+      </c>
+      <c r="R108">
+        <v>0</v>
+      </c>
+      <c r="S108">
+        <v>1073</v>
+      </c>
+      <c r="T108">
+        <v>0</v>
+      </c>
+      <c r="U108" s="5">
+        <f t="shared" si="5"/>
+        <v>13952</v>
+      </c>
+      <c r="W108" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB108">
+        <v>146</v>
+      </c>
+      <c r="AD108" s="5">
+        <f t="shared" si="7"/>
+        <v>14098</v>
+      </c>
+      <c r="AE108">
+        <v>1546</v>
+      </c>
+      <c r="AF108">
+        <v>97</v>
+      </c>
+      <c r="AG108">
+        <v>28</v>
+      </c>
+      <c r="AJ108" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL108" s="5">
+        <f t="shared" si="9"/>
+        <v>1671</v>
+      </c>
+      <c r="AM108" s="5">
+        <f t="shared" si="10"/>
+        <v>12427</v>
+      </c>
+    </row>
+    <row r="109" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A109" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="B109" t="s">
+        <v>2</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="E109" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F109" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G109" s="20" t="s">
+        <v>518</v>
+      </c>
+      <c r="H109" s="25">
+        <v>102345184043</v>
+      </c>
+      <c r="I109" s="25">
+        <v>1818150147</v>
+      </c>
+      <c r="J109" s="12">
+        <v>26</v>
+      </c>
+      <c r="K109">
+        <v>24</v>
+      </c>
+      <c r="L109" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M109" s="29"/>
+      <c r="N109" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P109">
+        <v>16489</v>
+      </c>
+      <c r="Q109">
+        <v>14050</v>
+      </c>
+      <c r="R109">
+        <v>0</v>
+      </c>
+      <c r="S109">
+        <v>1170</v>
+      </c>
+      <c r="T109">
+        <v>0</v>
+      </c>
+      <c r="U109" s="5">
+        <f t="shared" si="5"/>
+        <v>15220</v>
+      </c>
+      <c r="W109" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB109">
+        <v>0</v>
+      </c>
+      <c r="AD109" s="5">
+        <f t="shared" si="7"/>
+        <v>15220</v>
+      </c>
+      <c r="AE109">
+        <v>1686</v>
+      </c>
+      <c r="AF109">
+        <v>105</v>
+      </c>
+      <c r="AG109">
+        <v>30</v>
+      </c>
+      <c r="AJ109" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL109" s="5">
+        <f t="shared" si="9"/>
+        <v>1821</v>
+      </c>
+      <c r="AM109" s="5">
+        <f t="shared" si="10"/>
+        <v>13399</v>
+      </c>
+    </row>
+    <row r="110" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A110" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="B110" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E110" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F110" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G110" s="20" t="s">
+        <v>519</v>
+      </c>
+      <c r="H110" s="25">
+        <v>102066961098</v>
+      </c>
+      <c r="I110" s="25">
+        <v>2019740019</v>
+      </c>
+      <c r="J110" s="12">
+        <v>26</v>
+      </c>
+      <c r="K110">
+        <v>24</v>
+      </c>
+      <c r="L110" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M110" s="29"/>
+      <c r="N110" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P110">
+        <v>16489</v>
+      </c>
+      <c r="Q110">
+        <v>14050</v>
+      </c>
+      <c r="R110">
+        <v>0</v>
+      </c>
+      <c r="S110">
+        <v>1170</v>
+      </c>
+      <c r="T110">
+        <v>0</v>
+      </c>
+      <c r="U110" s="5">
+        <f t="shared" si="5"/>
+        <v>15220</v>
+      </c>
+      <c r="W110" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB110">
+        <v>0</v>
+      </c>
+      <c r="AD110" s="5">
+        <f t="shared" si="7"/>
+        <v>15220</v>
+      </c>
+      <c r="AE110">
+        <v>1686</v>
+      </c>
+      <c r="AF110">
+        <v>105</v>
+      </c>
+      <c r="AG110">
+        <v>30</v>
+      </c>
+      <c r="AJ110" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL110" s="5">
+        <f t="shared" si="9"/>
+        <v>1821</v>
+      </c>
+      <c r="AM110" s="5">
+        <f t="shared" si="10"/>
+        <v>13399</v>
+      </c>
+    </row>
+    <row r="111" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A111" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="E111" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F111" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G111" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="H111" s="25">
+        <v>101782933155</v>
+      </c>
+      <c r="I111" s="25">
+        <v>6932399993</v>
+      </c>
+      <c r="J111" s="12">
+        <v>26</v>
+      </c>
+      <c r="K111">
+        <v>25</v>
+      </c>
+      <c r="L111" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M111" s="29"/>
+      <c r="N111" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P111">
+        <v>16489</v>
+      </c>
+      <c r="Q111">
+        <v>14636</v>
+      </c>
+      <c r="R111">
+        <v>0</v>
+      </c>
+      <c r="S111">
+        <v>1219</v>
+      </c>
+      <c r="T111">
+        <v>0</v>
+      </c>
+      <c r="U111" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W111" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB111">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="5">
+        <f t="shared" si="7"/>
+        <v>15855</v>
+      </c>
+      <c r="AE111">
+        <v>1756</v>
+      </c>
+      <c r="AF111">
+        <v>110</v>
+      </c>
+      <c r="AG111">
+        <v>32</v>
+      </c>
+      <c r="AJ111" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="5">
+        <f t="shared" si="9"/>
+        <v>1898</v>
+      </c>
+      <c r="AM111" s="5">
+        <f t="shared" si="10"/>
+        <v>13957</v>
+      </c>
+    </row>
+    <row r="112" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A112" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="E112" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F112" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G112" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="H112" s="25">
+        <v>101460497143</v>
+      </c>
+      <c r="I112" s="25">
+        <v>6932400000</v>
+      </c>
+      <c r="J112" s="12">
+        <v>26</v>
+      </c>
+      <c r="K112">
+        <v>25</v>
+      </c>
+      <c r="L112" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M112" s="29"/>
+      <c r="N112" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P112">
+        <v>16489</v>
+      </c>
+      <c r="Q112">
+        <v>14636</v>
+      </c>
+      <c r="R112">
+        <v>0</v>
+      </c>
+      <c r="S112">
+        <v>1219</v>
+      </c>
+      <c r="T112">
+        <v>0</v>
+      </c>
+      <c r="U112" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W112" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB112">
+        <v>0</v>
+      </c>
+      <c r="AD112" s="5">
+        <f t="shared" si="7"/>
+        <v>15855</v>
+      </c>
+      <c r="AE112">
+        <v>1756</v>
+      </c>
+      <c r="AF112">
+        <v>110</v>
+      </c>
+      <c r="AG112">
+        <v>32</v>
+      </c>
+      <c r="AJ112" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL112" s="5">
+        <f t="shared" si="9"/>
+        <v>1898</v>
+      </c>
+      <c r="AM112" s="5">
+        <f t="shared" si="10"/>
+        <v>13957</v>
+      </c>
+    </row>
+    <row r="113" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A113" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="E113" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F113" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G113" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="H113" s="25">
+        <v>101821104147</v>
+      </c>
+      <c r="I113" s="25">
+        <v>6932336476</v>
+      </c>
+      <c r="J113" s="12">
+        <v>26</v>
+      </c>
+      <c r="K113">
+        <v>25</v>
+      </c>
+      <c r="L113" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M113" s="29"/>
+      <c r="N113" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P113">
+        <v>16489</v>
+      </c>
+      <c r="Q113">
+        <v>14636</v>
+      </c>
+      <c r="R113">
+        <v>0</v>
+      </c>
+      <c r="S113">
+        <v>1219</v>
+      </c>
+      <c r="T113">
+        <v>0</v>
+      </c>
+      <c r="U113" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W113" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB113">
+        <v>0</v>
+      </c>
+      <c r="AD113" s="5">
+        <f t="shared" si="7"/>
+        <v>15855</v>
+      </c>
+      <c r="AE113">
+        <v>1756</v>
+      </c>
+      <c r="AF113">
+        <v>110</v>
+      </c>
+      <c r="AG113">
+        <v>32</v>
+      </c>
+      <c r="AJ113" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL113" s="5">
+        <f t="shared" si="9"/>
+        <v>1898</v>
+      </c>
+      <c r="AM113" s="5">
+        <f t="shared" si="10"/>
+        <v>13957</v>
+      </c>
+    </row>
+    <row r="114" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A114" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="B114" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="E114" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F114" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G114" s="20" t="s">
+        <v>523</v>
+      </c>
+      <c r="H114" s="25">
+        <v>101616606034</v>
+      </c>
+      <c r="I114" s="25">
+        <v>2018097763</v>
+      </c>
+      <c r="J114" s="12">
+        <v>26</v>
+      </c>
+      <c r="K114">
+        <v>25</v>
+      </c>
+      <c r="L114" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M114" s="29"/>
+      <c r="N114" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P114">
+        <v>16489</v>
+      </c>
+      <c r="Q114">
+        <v>14636</v>
+      </c>
+      <c r="R114">
+        <v>0</v>
+      </c>
+      <c r="S114">
+        <v>1219</v>
+      </c>
+      <c r="T114">
+        <v>0</v>
+      </c>
+      <c r="U114" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W114" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB114">
+        <v>0</v>
+      </c>
+      <c r="AD114" s="5">
+        <f t="shared" si="7"/>
+        <v>15855</v>
+      </c>
+      <c r="AE114">
+        <v>1756</v>
+      </c>
+      <c r="AF114">
+        <v>110</v>
+      </c>
+      <c r="AG114">
+        <v>32</v>
+      </c>
+      <c r="AJ114" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL114" s="5">
+        <f t="shared" si="9"/>
+        <v>1898</v>
+      </c>
+      <c r="AM114" s="5">
+        <f t="shared" si="10"/>
+        <v>13957</v>
+      </c>
+    </row>
+    <row r="115" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A115" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B115" t="s">
+        <v>2</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E115" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F115" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G115" s="20" t="s">
+        <v>524</v>
+      </c>
+      <c r="H115" s="25">
+        <v>102025022499</v>
+      </c>
+      <c r="I115" s="25">
+        <v>2019866907</v>
+      </c>
+      <c r="J115" s="12">
+        <v>26</v>
+      </c>
+      <c r="K115">
+        <v>25</v>
+      </c>
+      <c r="L115" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M115" s="29"/>
+      <c r="N115" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P115">
+        <v>16489</v>
+      </c>
+      <c r="Q115">
+        <v>14636</v>
+      </c>
+      <c r="R115">
+        <v>0</v>
+      </c>
+      <c r="S115">
+        <v>1219</v>
+      </c>
+      <c r="T115">
+        <v>0</v>
+      </c>
+      <c r="U115" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W115" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB115">
+        <v>0</v>
+      </c>
+      <c r="AD115" s="5">
+        <f t="shared" si="7"/>
+        <v>15855</v>
+      </c>
+      <c r="AE115">
+        <v>1756</v>
+      </c>
+      <c r="AF115">
+        <v>110</v>
+      </c>
+      <c r="AG115">
+        <v>32</v>
+      </c>
+      <c r="AJ115" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL115" s="5">
+        <f t="shared" si="9"/>
+        <v>1898</v>
+      </c>
+      <c r="AM115" s="5">
+        <f t="shared" si="10"/>
+        <v>13957</v>
+      </c>
+    </row>
+    <row r="116" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A116" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B116" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="E116" s="31" t="s">
+        <v>567</v>
+      </c>
+      <c r="F116" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G116" s="20" t="s">
+        <v>525</v>
+      </c>
+      <c r="H116" s="25">
+        <v>101863970652</v>
+      </c>
+      <c r="I116" s="25">
+        <v>2214907813</v>
+      </c>
+      <c r="J116" s="12">
+        <v>26</v>
+      </c>
+      <c r="K116">
+        <v>25</v>
+      </c>
+      <c r="L116" s="28">
+        <v>16781</v>
+      </c>
+      <c r="M116" s="29">
+        <v>3000</v>
+      </c>
+      <c r="N116" s="29">
+        <v>1398</v>
+      </c>
+      <c r="P116">
+        <v>21179</v>
+      </c>
+      <c r="Q116">
+        <v>16136</v>
+      </c>
+      <c r="R116">
+        <v>2885</v>
+      </c>
+      <c r="S116">
+        <v>1344</v>
+      </c>
+      <c r="T116">
+        <v>0</v>
+      </c>
+      <c r="U116" s="5">
+        <f t="shared" si="5"/>
+        <v>20365</v>
+      </c>
+      <c r="W116" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB116">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="5">
+        <f t="shared" si="7"/>
+        <v>20365</v>
+      </c>
+      <c r="AE116">
+        <v>1936</v>
+      </c>
+      <c r="AF116">
+        <v>121</v>
+      </c>
+      <c r="AG116">
+        <v>35</v>
+      </c>
+      <c r="AJ116" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL116" s="5">
+        <f t="shared" si="9"/>
+        <v>2092</v>
+      </c>
+      <c r="AM116" s="5">
+        <f t="shared" si="10"/>
+        <v>18273</v>
+      </c>
+    </row>
+    <row r="117" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A117" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B117" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="E117" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F117" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G117" s="20" t="s">
+        <v>526</v>
+      </c>
+      <c r="H117" s="25">
+        <v>101541495439</v>
+      </c>
+      <c r="I117" s="25">
+        <v>2017797675</v>
+      </c>
+      <c r="J117" s="12">
+        <v>26</v>
+      </c>
+      <c r="K117">
+        <v>25</v>
+      </c>
+      <c r="L117" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M117" s="29"/>
+      <c r="N117" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P117">
+        <v>16489</v>
+      </c>
+      <c r="Q117">
+        <v>14636</v>
+      </c>
+      <c r="R117">
+        <v>0</v>
+      </c>
+      <c r="S117">
+        <v>1219</v>
+      </c>
+      <c r="T117">
+        <v>0</v>
+      </c>
+      <c r="U117" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W117" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB117">
+        <v>0</v>
+      </c>
+      <c r="AD117" s="5">
+        <f t="shared" si="7"/>
+        <v>15855</v>
+      </c>
+      <c r="AE117">
+        <v>1756</v>
+      </c>
+      <c r="AF117">
+        <v>110</v>
+      </c>
+      <c r="AG117">
+        <v>32</v>
+      </c>
+      <c r="AJ117" s="20">
+        <v>2500</v>
+      </c>
+      <c r="AL117" s="5">
+        <f t="shared" si="9"/>
+        <v>4398</v>
+      </c>
+      <c r="AM117" s="5">
+        <f t="shared" si="10"/>
+        <v>11457</v>
+      </c>
+    </row>
+    <row r="118" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A118" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="B118" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E118" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F118" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G118" s="20" t="s">
+        <v>527</v>
+      </c>
+      <c r="H118" s="25">
+        <v>101855129216</v>
+      </c>
+      <c r="I118" s="26">
+        <v>2019693394</v>
+      </c>
+      <c r="J118" s="12">
+        <v>26</v>
+      </c>
+      <c r="K118">
+        <v>25</v>
+      </c>
+      <c r="L118" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M118" s="29"/>
+      <c r="N118" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P118">
+        <v>16489</v>
+      </c>
+      <c r="Q118">
+        <v>14636</v>
+      </c>
+      <c r="R118">
+        <v>0</v>
+      </c>
+      <c r="S118">
+        <v>1219</v>
+      </c>
+      <c r="T118">
+        <v>0</v>
+      </c>
+      <c r="U118" s="5">
+        <f t="shared" si="5"/>
+        <v>15855</v>
+      </c>
+      <c r="W118" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB118">
+        <v>585</v>
+      </c>
+      <c r="AD118" s="5">
+        <f t="shared" si="7"/>
+        <v>16440</v>
+      </c>
+      <c r="AE118">
+        <v>1756</v>
+      </c>
+      <c r="AF118">
+        <v>110</v>
+      </c>
+      <c r="AG118">
+        <v>32</v>
+      </c>
+      <c r="AJ118" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL118" s="5">
+        <f t="shared" si="9"/>
+        <v>1898</v>
+      </c>
+      <c r="AM118" s="5">
+        <f t="shared" si="10"/>
+        <v>14542</v>
+      </c>
+    </row>
+    <row r="119" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A119" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="B119" t="s">
+        <v>2</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="E119" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F119" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G119" s="20" t="s">
+        <v>528</v>
+      </c>
+      <c r="H119" s="25">
+        <v>101781524134</v>
+      </c>
+      <c r="I119" s="25">
+        <v>2019935463</v>
+      </c>
+      <c r="J119" s="12">
+        <v>26</v>
+      </c>
+      <c r="K119">
+        <v>25.5</v>
+      </c>
+      <c r="L119" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M119" s="29"/>
+      <c r="N119" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P119">
+        <v>16489</v>
+      </c>
+      <c r="Q119">
+        <v>14928</v>
+      </c>
+      <c r="R119">
+        <v>0</v>
+      </c>
+      <c r="S119">
+        <v>1244</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+      <c r="U119" s="5">
+        <f t="shared" si="5"/>
+        <v>16172</v>
+      </c>
+      <c r="W119" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB119">
+        <v>0</v>
+      </c>
+      <c r="AD119" s="5">
+        <f t="shared" si="7"/>
+        <v>16172</v>
+      </c>
+      <c r="AE119">
+        <v>1791</v>
+      </c>
+      <c r="AF119">
+        <v>112</v>
+      </c>
+      <c r="AG119">
+        <v>32</v>
+      </c>
+      <c r="AJ119" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL119" s="5">
+        <f t="shared" si="9"/>
+        <v>1935</v>
+      </c>
+      <c r="AM119" s="5">
+        <f t="shared" si="10"/>
+        <v>14237</v>
+      </c>
+    </row>
+    <row r="120" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A120" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B120" t="s">
+        <v>2</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="E120" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F120" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G120" s="20" t="s">
+        <v>529</v>
+      </c>
+      <c r="H120" s="25">
+        <v>101682622745</v>
+      </c>
+      <c r="I120" s="25">
+        <v>6932400027</v>
+      </c>
+      <c r="J120" s="12">
+        <v>26</v>
+      </c>
+      <c r="K120">
+        <v>26</v>
+      </c>
+      <c r="L120" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M120" s="29"/>
+      <c r="N120" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P120">
+        <v>16489</v>
+      </c>
+      <c r="Q120">
+        <v>15221</v>
+      </c>
+      <c r="R120">
+        <v>0</v>
+      </c>
+      <c r="S120">
+        <v>1268</v>
+      </c>
+      <c r="T120">
+        <v>0</v>
+      </c>
+      <c r="U120" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W120" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB120">
+        <v>0</v>
+      </c>
+      <c r="AD120" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE120">
+        <v>1827</v>
+      </c>
+      <c r="AF120">
+        <v>114</v>
+      </c>
+      <c r="AG120">
+        <v>33</v>
+      </c>
+      <c r="AJ120" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL120" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM120" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="121" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A121" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B121" t="s">
+        <v>2</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="E121" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F121" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G121" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="H121" s="25">
+        <v>101264000928</v>
+      </c>
+      <c r="I121" s="25">
+        <v>6932399733</v>
+      </c>
+      <c r="J121" s="12">
+        <v>26</v>
+      </c>
+      <c r="K121">
+        <v>26</v>
+      </c>
+      <c r="L121" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M121" s="29"/>
+      <c r="N121" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P121">
+        <v>16489</v>
+      </c>
+      <c r="Q121">
+        <v>15221</v>
+      </c>
+      <c r="R121">
+        <v>0</v>
+      </c>
+      <c r="S121">
+        <v>1268</v>
+      </c>
+      <c r="T121">
+        <v>0</v>
+      </c>
+      <c r="U121" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W121" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB121">
+        <v>439</v>
+      </c>
+      <c r="AD121" s="5">
+        <f t="shared" si="7"/>
+        <v>17628</v>
+      </c>
+      <c r="AE121">
+        <v>1827</v>
+      </c>
+      <c r="AF121">
+        <v>114</v>
+      </c>
+      <c r="AG121">
+        <v>33</v>
+      </c>
+      <c r="AJ121" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL121" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM121" s="5">
+        <f t="shared" si="10"/>
+        <v>15654</v>
+      </c>
+    </row>
+    <row r="122" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A122" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="B122" t="s">
+        <v>2</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="E122" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F122" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G122" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="H122" s="25">
+        <v>101997272018</v>
+      </c>
+      <c r="I122" s="25">
+        <v>2019693395</v>
+      </c>
+      <c r="J122" s="12">
+        <v>26</v>
+      </c>
+      <c r="K122">
+        <v>26</v>
+      </c>
+      <c r="L122" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M122" s="29"/>
+      <c r="N122" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P122">
+        <v>16489</v>
+      </c>
+      <c r="Q122">
+        <v>15221</v>
+      </c>
+      <c r="R122">
+        <v>0</v>
+      </c>
+      <c r="S122">
+        <v>1268</v>
+      </c>
+      <c r="T122">
+        <v>0</v>
+      </c>
+      <c r="U122" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W122" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB122">
+        <v>0</v>
+      </c>
+      <c r="AD122" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE122">
+        <v>1827</v>
+      </c>
+      <c r="AF122">
+        <v>114</v>
+      </c>
+      <c r="AG122">
+        <v>33</v>
+      </c>
+      <c r="AJ122" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL122" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM122" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="123" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A123" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="B123" t="s">
+        <v>2</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="E123" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F123" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G123" s="20" t="s">
+        <v>532</v>
+      </c>
+      <c r="H123" s="25">
+        <v>101975155289</v>
+      </c>
+      <c r="I123" s="25">
+        <v>2019693392</v>
+      </c>
+      <c r="J123" s="12">
+        <v>26</v>
+      </c>
+      <c r="K123">
+        <v>26</v>
+      </c>
+      <c r="L123" s="28">
+        <v>16781</v>
+      </c>
+      <c r="M123" s="29"/>
+      <c r="N123" s="29">
+        <v>1398</v>
+      </c>
+      <c r="P123">
+        <v>18179</v>
+      </c>
+      <c r="Q123">
+        <v>16781</v>
+      </c>
+      <c r="R123">
+        <v>0</v>
+      </c>
+      <c r="S123">
+        <v>1398</v>
+      </c>
+      <c r="T123">
+        <v>0</v>
+      </c>
+      <c r="U123" s="5">
+        <f t="shared" si="5"/>
+        <v>18179</v>
+      </c>
+      <c r="W123" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB123">
+        <v>0</v>
+      </c>
+      <c r="AD123" s="5">
+        <f t="shared" si="7"/>
+        <v>18879</v>
+      </c>
+      <c r="AE123">
+        <v>2014</v>
+      </c>
+      <c r="AF123">
+        <v>126</v>
+      </c>
+      <c r="AG123">
+        <v>35</v>
+      </c>
+      <c r="AJ123" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL123" s="5">
+        <f t="shared" si="9"/>
+        <v>2175</v>
+      </c>
+      <c r="AM123" s="5">
+        <f t="shared" si="10"/>
+        <v>16704</v>
+      </c>
+    </row>
+    <row r="124" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A124" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="B124" t="s">
+        <v>2</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="E124" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F124" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G124" s="20" t="s">
+        <v>533</v>
+      </c>
+      <c r="H124" s="25">
+        <v>101416378667</v>
+      </c>
+      <c r="I124" s="25">
+        <v>6934027302</v>
+      </c>
+      <c r="J124" s="12">
+        <v>26</v>
+      </c>
+      <c r="K124">
+        <v>26</v>
+      </c>
+      <c r="L124" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M124" s="29"/>
+      <c r="N124" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P124">
+        <v>16489</v>
+      </c>
+      <c r="Q124">
+        <v>15221</v>
+      </c>
+      <c r="R124">
+        <v>0</v>
+      </c>
+      <c r="S124">
+        <v>1268</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+      <c r="U124" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W124" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB124">
+        <v>0</v>
+      </c>
+      <c r="AD124" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE124">
+        <v>1827</v>
+      </c>
+      <c r="AF124">
+        <v>114</v>
+      </c>
+      <c r="AG124">
+        <v>33</v>
+      </c>
+      <c r="AJ124" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL124" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM124" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="125" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A125" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B125" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="E125" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F125" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G125" s="20" t="s">
+        <v>534</v>
+      </c>
+      <c r="H125" s="25">
+        <v>101820153853</v>
+      </c>
+      <c r="I125" s="25">
+        <v>6933908691</v>
+      </c>
+      <c r="J125" s="12">
+        <v>26</v>
+      </c>
+      <c r="K125">
+        <v>26</v>
+      </c>
+      <c r="L125" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M125" s="29"/>
+      <c r="N125" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P125">
+        <v>16489</v>
+      </c>
+      <c r="Q125">
+        <v>15221</v>
+      </c>
+      <c r="R125">
+        <v>0</v>
+      </c>
+      <c r="S125">
+        <v>1268</v>
+      </c>
+      <c r="T125">
+        <v>0</v>
+      </c>
+      <c r="U125" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W125" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB125">
+        <v>0</v>
+      </c>
+      <c r="AD125" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE125">
+        <v>1827</v>
+      </c>
+      <c r="AF125">
+        <v>114</v>
+      </c>
+      <c r="AG125">
+        <v>33</v>
+      </c>
+      <c r="AJ125" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL125" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM125" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="126" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A126" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="B126" t="s">
+        <v>2</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="E126" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F126" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G126" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="H126" s="25">
+        <v>101943668524</v>
+      </c>
+      <c r="I126" s="25">
+        <v>6934010954</v>
+      </c>
+      <c r="J126" s="12">
+        <v>26</v>
+      </c>
+      <c r="K126">
+        <v>26</v>
+      </c>
+      <c r="L126" s="28">
+        <v>16781</v>
+      </c>
+      <c r="M126" s="29"/>
+      <c r="N126" s="29">
+        <v>1398</v>
+      </c>
+      <c r="P126">
+        <v>18179</v>
+      </c>
+      <c r="Q126">
+        <v>16781</v>
+      </c>
+      <c r="R126">
+        <v>0</v>
+      </c>
+      <c r="S126">
+        <v>1398</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+      <c r="U126" s="5">
+        <f t="shared" si="5"/>
+        <v>18179</v>
+      </c>
+      <c r="W126" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB126">
+        <v>0</v>
+      </c>
+      <c r="AD126" s="5">
+        <f t="shared" si="7"/>
+        <v>18879</v>
+      </c>
+      <c r="AE126">
+        <v>2014</v>
+      </c>
+      <c r="AF126">
+        <v>126</v>
+      </c>
+      <c r="AG126">
+        <v>35</v>
+      </c>
+      <c r="AJ126" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL126" s="5">
+        <f t="shared" si="9"/>
+        <v>2175</v>
+      </c>
+      <c r="AM126" s="5">
+        <f t="shared" si="10"/>
+        <v>16704</v>
+      </c>
+    </row>
+    <row r="127" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A127" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="B127" t="s">
+        <v>2</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="E127" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F127" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G127" s="20" t="s">
+        <v>536</v>
+      </c>
+      <c r="H127" s="25">
+        <v>101995548786</v>
+      </c>
+      <c r="I127" s="25">
+        <v>6934010918</v>
+      </c>
+      <c r="J127" s="12">
+        <v>26</v>
+      </c>
+      <c r="K127">
+        <v>26</v>
+      </c>
+      <c r="L127" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M127" s="29"/>
+      <c r="N127" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P127">
+        <v>16489</v>
+      </c>
+      <c r="Q127">
+        <v>15221</v>
+      </c>
+      <c r="R127">
+        <v>0</v>
+      </c>
+      <c r="S127">
+        <v>1268</v>
+      </c>
+      <c r="T127">
+        <v>0</v>
+      </c>
+      <c r="U127" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W127" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB127">
+        <v>439</v>
+      </c>
+      <c r="AD127" s="5">
+        <f t="shared" si="7"/>
+        <v>17628</v>
+      </c>
+      <c r="AE127">
+        <v>1827</v>
+      </c>
+      <c r="AF127">
+        <v>114</v>
+      </c>
+      <c r="AG127">
+        <v>33</v>
+      </c>
+      <c r="AJ127" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL127" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM127" s="5">
+        <f t="shared" si="10"/>
+        <v>15654</v>
+      </c>
+    </row>
+    <row r="128" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A128" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="B128" t="s">
+        <v>2</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="E128" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F128" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G128" s="20" t="s">
+        <v>537</v>
+      </c>
+      <c r="H128" s="25">
+        <v>101909726499</v>
+      </c>
+      <c r="I128" s="25">
+        <v>2019693388</v>
+      </c>
+      <c r="J128" s="12">
+        <v>26</v>
+      </c>
+      <c r="K128">
+        <v>26</v>
+      </c>
+      <c r="L128" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M128" s="29"/>
+      <c r="N128" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P128">
+        <v>16489</v>
+      </c>
+      <c r="Q128">
+        <v>15221</v>
+      </c>
+      <c r="R128">
+        <v>0</v>
+      </c>
+      <c r="S128">
+        <v>1268</v>
+      </c>
+      <c r="T128">
+        <v>0</v>
+      </c>
+      <c r="U128" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W128" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB128">
+        <v>0</v>
+      </c>
+      <c r="AD128" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE128">
+        <v>1827</v>
+      </c>
+      <c r="AF128">
+        <v>114</v>
+      </c>
+      <c r="AG128">
+        <v>33</v>
+      </c>
+      <c r="AJ128" s="20">
+        <v>2000</v>
+      </c>
+      <c r="AL128" s="5">
+        <f t="shared" si="9"/>
+        <v>3974</v>
+      </c>
+      <c r="AM128" s="5">
+        <f t="shared" si="10"/>
+        <v>13215</v>
+      </c>
+    </row>
+    <row r="129" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A129" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="B129" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="E129" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F129" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G129" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="H129" s="25">
+        <v>101686918579</v>
+      </c>
+      <c r="I129" s="25">
+        <v>5348366238</v>
+      </c>
+      <c r="J129" s="12">
+        <v>26</v>
+      </c>
+      <c r="K129">
+        <v>26</v>
+      </c>
+      <c r="L129" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M129" s="29"/>
+      <c r="N129" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P129">
+        <v>16489</v>
+      </c>
+      <c r="Q129">
+        <v>15221</v>
+      </c>
+      <c r="R129">
+        <v>0</v>
+      </c>
+      <c r="S129">
+        <v>1268</v>
+      </c>
+      <c r="T129">
+        <v>0</v>
+      </c>
+      <c r="U129" s="5">
+        <f t="shared" si="5"/>
+        <v>16489</v>
+      </c>
+      <c r="W129" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB129">
+        <v>0</v>
+      </c>
+      <c r="AD129" s="5">
+        <f t="shared" si="7"/>
+        <v>17189</v>
+      </c>
+      <c r="AE129">
+        <v>1827</v>
+      </c>
+      <c r="AF129">
+        <v>114</v>
+      </c>
+      <c r="AG129">
+        <v>33</v>
+      </c>
+      <c r="AJ129" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL129" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM129" s="5">
+        <f t="shared" si="10"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="130" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A130" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="B130" t="s">
+        <v>2</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E130" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F130" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G130" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="H130" s="25">
+        <v>101974375628</v>
+      </c>
+      <c r="I130" s="25">
+        <v>6935385957</v>
+      </c>
+      <c r="J130" s="12">
+        <v>26</v>
+      </c>
+      <c r="K130">
+        <v>26</v>
+      </c>
+      <c r="L130" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M130" s="29"/>
+      <c r="N130" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P130">
+        <v>16489</v>
+      </c>
+      <c r="Q130">
+        <v>15221</v>
+      </c>
+      <c r="R130">
+        <v>0</v>
+      </c>
+      <c r="S130">
+        <v>1268</v>
+      </c>
+      <c r="T130">
+        <v>0</v>
+      </c>
+      <c r="U130" s="5">
+        <f t="shared" ref="U130:U139" si="11">+ROUND(SUM(Q130:T130),0)</f>
+        <v>16489</v>
+      </c>
+      <c r="W130" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB130">
+        <v>732</v>
+      </c>
+      <c r="AD130" s="5">
+        <f t="shared" si="7"/>
+        <v>17921</v>
+      </c>
+      <c r="AE130">
+        <v>1827</v>
+      </c>
+      <c r="AF130">
+        <v>114</v>
+      </c>
+      <c r="AG130">
+        <v>33</v>
+      </c>
+      <c r="AJ130" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL130" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM130" s="5">
+        <f t="shared" si="10"/>
+        <v>15947</v>
+      </c>
+    </row>
+    <row r="131" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A131" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="B131" t="s">
+        <v>2</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="E131" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F131" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G131" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="H131" s="25">
+        <v>102183833375</v>
+      </c>
+      <c r="I131" s="25">
+        <v>6937329155</v>
+      </c>
+      <c r="J131" s="12">
+        <v>26</v>
+      </c>
+      <c r="K131">
+        <v>26</v>
+      </c>
+      <c r="L131" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M131" s="29"/>
+      <c r="N131" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P131">
+        <v>16489</v>
+      </c>
+      <c r="Q131">
+        <v>15221</v>
+      </c>
+      <c r="R131">
+        <v>0</v>
+      </c>
+      <c r="S131">
+        <v>1268</v>
+      </c>
+      <c r="T131">
+        <v>0</v>
+      </c>
+      <c r="U131" s="5">
+        <f t="shared" si="11"/>
+        <v>16489</v>
+      </c>
+      <c r="W131" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB131">
+        <v>585</v>
+      </c>
+      <c r="AD131" s="5">
+        <f t="shared" ref="AD131:AD139" si="12">+U131+AA131+AB131+AC131+V131+W131+X131+Y131+Z131</f>
+        <v>17774</v>
+      </c>
+      <c r="AE131">
+        <v>1827</v>
+      </c>
+      <c r="AF131">
+        <v>114</v>
+      </c>
+      <c r="AG131">
+        <v>33</v>
+      </c>
+      <c r="AJ131" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL131" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM131" s="5">
+        <f t="shared" si="10"/>
+        <v>15800</v>
+      </c>
+    </row>
+    <row r="132" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A132" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="B132" t="s">
+        <v>2</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="E132" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F132" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G132" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="H132" s="25">
+        <v>102183833381</v>
+      </c>
+      <c r="I132" s="25">
+        <v>6937329209</v>
+      </c>
+      <c r="J132" s="12">
+        <v>26</v>
+      </c>
+      <c r="K132">
+        <v>26</v>
+      </c>
+      <c r="L132" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M132" s="29"/>
+      <c r="N132" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P132">
+        <v>16489</v>
+      </c>
+      <c r="Q132">
+        <v>15221</v>
+      </c>
+      <c r="R132">
+        <v>0</v>
+      </c>
+      <c r="S132">
+        <v>1268</v>
+      </c>
+      <c r="T132">
+        <v>0</v>
+      </c>
+      <c r="U132" s="5">
+        <f t="shared" si="11"/>
+        <v>16489</v>
+      </c>
+      <c r="W132" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB132">
+        <v>878</v>
+      </c>
+      <c r="AD132" s="5">
+        <f t="shared" si="12"/>
+        <v>18067</v>
+      </c>
+      <c r="AE132">
+        <v>1827</v>
+      </c>
+      <c r="AF132">
+        <v>114</v>
+      </c>
+      <c r="AG132">
+        <v>33</v>
+      </c>
+      <c r="AJ132" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL132" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM132" s="5">
+        <f t="shared" si="10"/>
+        <v>16093</v>
+      </c>
+    </row>
+    <row r="133" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A133" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="B133" t="s">
+        <v>2</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="E133" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F133" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G133" s="20" t="s">
+        <v>542</v>
+      </c>
+      <c r="H133" s="25">
+        <v>102183833334</v>
+      </c>
+      <c r="I133" s="25">
+        <v>6937329285</v>
+      </c>
+      <c r="J133" s="12">
+        <v>26</v>
+      </c>
+      <c r="K133">
+        <v>26</v>
+      </c>
+      <c r="L133" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M133" s="29"/>
+      <c r="N133" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P133">
+        <v>16489</v>
+      </c>
+      <c r="Q133">
+        <v>15221</v>
+      </c>
+      <c r="R133">
+        <v>0</v>
+      </c>
+      <c r="S133">
+        <v>1268</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+      <c r="U133" s="5">
+        <f t="shared" si="11"/>
+        <v>16489</v>
+      </c>
+      <c r="W133" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB133">
+        <v>732</v>
+      </c>
+      <c r="AD133" s="5">
+        <f t="shared" si="12"/>
+        <v>17921</v>
+      </c>
+      <c r="AE133">
+        <v>1827</v>
+      </c>
+      <c r="AF133">
+        <v>114</v>
+      </c>
+      <c r="AG133">
+        <v>33</v>
+      </c>
+      <c r="AJ133" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL133" s="5">
+        <f t="shared" si="9"/>
+        <v>1974</v>
+      </c>
+      <c r="AM133" s="5">
+        <f t="shared" si="10"/>
+        <v>15947</v>
+      </c>
+    </row>
+    <row r="134" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A134" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B134" t="s">
+        <v>2</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="E134" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F134" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G134" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="H134" s="25">
+        <v>101996468149</v>
+      </c>
+      <c r="I134" s="25">
+        <v>6934018961</v>
+      </c>
+      <c r="J134" s="12">
+        <v>26</v>
+      </c>
+      <c r="K134">
+        <v>26</v>
+      </c>
+      <c r="L134" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M134" s="29"/>
+      <c r="N134" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P134">
+        <v>16489</v>
+      </c>
+      <c r="Q134">
+        <v>15221</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+      <c r="S134">
+        <v>1268</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134" s="5">
+        <f t="shared" si="11"/>
+        <v>16489</v>
+      </c>
+      <c r="W134" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB134">
+        <v>0</v>
+      </c>
+      <c r="AD134" s="5">
+        <f t="shared" si="12"/>
+        <v>17189</v>
+      </c>
+      <c r="AE134">
+        <v>1827</v>
+      </c>
+      <c r="AF134">
+        <v>114</v>
+      </c>
+      <c r="AG134">
+        <v>33</v>
+      </c>
+      <c r="AJ134" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL134" s="5">
+        <f t="shared" ref="AL134:AL139" si="13">+ROUND(AJ134+AI134+AG134+AF134+AE134+AK134,0)+AH134</f>
+        <v>1974</v>
+      </c>
+      <c r="AM134" s="5">
+        <f t="shared" ref="AM134:AM139" si="14">+AD134-AL134</f>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="135" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A135" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B135" t="s">
+        <v>2</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="E135" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F135" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G135" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="H135" s="25">
+        <v>101997205853</v>
+      </c>
+      <c r="I135" s="25">
+        <v>2019914205</v>
+      </c>
+      <c r="J135" s="12">
+        <v>26</v>
+      </c>
+      <c r="K135">
+        <v>26</v>
+      </c>
+      <c r="L135" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M135" s="29"/>
+      <c r="N135" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P135">
+        <v>16489</v>
+      </c>
+      <c r="Q135">
+        <v>15221</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+      <c r="S135">
+        <v>1268</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135" s="5">
+        <f t="shared" si="11"/>
+        <v>16489</v>
+      </c>
+      <c r="W135" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB135">
+        <v>0</v>
+      </c>
+      <c r="AD135" s="5">
+        <f t="shared" si="12"/>
+        <v>17189</v>
+      </c>
+      <c r="AE135">
+        <v>1827</v>
+      </c>
+      <c r="AF135">
+        <v>114</v>
+      </c>
+      <c r="AG135">
+        <v>33</v>
+      </c>
+      <c r="AJ135" s="20">
+        <v>3500</v>
+      </c>
+      <c r="AL135" s="5">
+        <f t="shared" si="13"/>
+        <v>5474</v>
+      </c>
+      <c r="AM135" s="5">
+        <f t="shared" si="14"/>
+        <v>11715</v>
+      </c>
+    </row>
+    <row r="136" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A136" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="B136" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="E136" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F136" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G136" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="H136" s="25">
+        <v>101171148075</v>
+      </c>
+      <c r="I136" s="25">
+        <v>6934027231</v>
+      </c>
+      <c r="J136" s="12">
+        <v>26</v>
+      </c>
+      <c r="K136">
+        <v>26</v>
+      </c>
+      <c r="L136" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M136" s="29"/>
+      <c r="N136" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P136">
+        <v>16489</v>
+      </c>
+      <c r="Q136">
+        <v>15221</v>
+      </c>
+      <c r="R136">
+        <v>0</v>
+      </c>
+      <c r="S136">
+        <v>1268</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="U136" s="5">
+        <f t="shared" si="11"/>
+        <v>16489</v>
+      </c>
+      <c r="W136" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB136">
+        <v>0</v>
+      </c>
+      <c r="AD136" s="5">
+        <f t="shared" si="12"/>
+        <v>17189</v>
+      </c>
+      <c r="AE136">
+        <v>1827</v>
+      </c>
+      <c r="AF136">
+        <v>114</v>
+      </c>
+      <c r="AG136">
+        <v>33</v>
+      </c>
+      <c r="AJ136" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL136" s="5">
+        <f t="shared" si="13"/>
+        <v>1974</v>
+      </c>
+      <c r="AM136" s="5">
+        <f t="shared" si="14"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="137" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A137" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="B137" t="s">
+        <v>2</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="E137" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F137" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G137" s="20" t="s">
+        <v>546</v>
+      </c>
+      <c r="H137" s="25">
+        <v>102370662014</v>
+      </c>
+      <c r="I137" s="26">
+        <v>6937391988</v>
+      </c>
+      <c r="J137" s="12">
+        <v>26</v>
+      </c>
+      <c r="K137">
+        <v>26</v>
+      </c>
+      <c r="L137" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M137" s="29"/>
+      <c r="N137" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P137">
+        <v>16489</v>
+      </c>
+      <c r="Q137">
+        <v>15221</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+      <c r="S137">
+        <v>1268</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137" s="5">
+        <f t="shared" si="11"/>
+        <v>16489</v>
+      </c>
+      <c r="W137" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AD137" s="5">
+        <f t="shared" si="12"/>
+        <v>17189</v>
+      </c>
+      <c r="AE137">
+        <v>1827</v>
+      </c>
+      <c r="AF137">
+        <v>114</v>
+      </c>
+      <c r="AG137">
+        <v>33</v>
+      </c>
+      <c r="AJ137" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL137" s="5">
+        <f t="shared" si="13"/>
+        <v>1974</v>
+      </c>
+      <c r="AM137" s="5">
+        <f t="shared" si="14"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="138" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A138" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="B138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="E138" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F138" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G138" s="20" t="s">
+        <v>547</v>
+      </c>
+      <c r="H138" s="25">
+        <v>102370265299</v>
+      </c>
+      <c r="I138" s="26">
+        <v>6937391977</v>
+      </c>
+      <c r="J138" s="12">
+        <v>26</v>
+      </c>
+      <c r="K138">
+        <v>26</v>
+      </c>
+      <c r="L138" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M138" s="29"/>
+      <c r="N138" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P138">
+        <v>16489</v>
+      </c>
+      <c r="Q138">
+        <v>15221</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+      <c r="S138">
+        <v>1268</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138" s="5">
+        <f t="shared" si="11"/>
+        <v>16489</v>
+      </c>
+      <c r="W138" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AD138" s="5">
+        <f t="shared" si="12"/>
+        <v>17189</v>
+      </c>
+      <c r="AE138">
+        <v>1827</v>
+      </c>
+      <c r="AF138">
+        <v>114</v>
+      </c>
+      <c r="AG138">
+        <v>33</v>
+      </c>
+      <c r="AJ138" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL138" s="5">
+        <f t="shared" si="13"/>
+        <v>1974</v>
+      </c>
+      <c r="AM138" s="5">
+        <f t="shared" si="14"/>
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="139" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A139" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="B139" t="s">
+        <v>2</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="E139" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="F139" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="G139" s="20" t="s">
+        <v>548</v>
+      </c>
+      <c r="H139" s="25">
+        <v>101988888031</v>
+      </c>
+      <c r="I139" s="25">
+        <v>6934018223</v>
+      </c>
+      <c r="J139" s="12">
+        <v>26</v>
+      </c>
+      <c r="K139">
+        <v>26</v>
+      </c>
+      <c r="L139" s="28">
+        <v>15221</v>
+      </c>
+      <c r="M139" s="29"/>
+      <c r="N139" s="29">
+        <v>1268</v>
+      </c>
+      <c r="P139">
+        <v>16489</v>
+      </c>
+      <c r="Q139">
+        <v>15221</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>1268</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139" s="5">
+        <f t="shared" si="11"/>
+        <v>16489</v>
+      </c>
+      <c r="W139" s="30">
+        <v>700</v>
+      </c>
+      <c r="AB139">
+        <v>585</v>
+      </c>
+      <c r="AD139" s="5">
+        <f t="shared" si="12"/>
+        <v>17774</v>
+      </c>
+      <c r="AE139">
+        <v>1827</v>
+      </c>
+      <c r="AF139">
+        <v>114</v>
+      </c>
+      <c r="AG139">
+        <v>33</v>
+      </c>
+      <c r="AJ139" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL139" s="5">
+        <f t="shared" si="13"/>
+        <v>1974</v>
+      </c>
+      <c r="AM139" s="5">
+        <f t="shared" si="14"/>
+        <v>15800</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="H117">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H121">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H71:H74 H76:H84 H89:H93 H95:H96 H99:H102 H105:H139">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>